--- a/Assets/Data/ZX Spectrum/Spectrum 16K-48K/Issue 4B/Data ZX 4B v2.0.0.xlsx
+++ b/Assets/Data/ZX Spectrum/Spectrum 16K-48K/Issue 4B/Data ZX 4B v2.0.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\ZX Spectrum\Spectrum 16K-48K\Issue 4B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data-BETA\Data\ZX Spectrum\Spectrum 16K-48K\Issue 4B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13F7BD8-D5B4-44E5-9FC0-C2BD6F882102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530507B7-997D-4C2A-A6D1-5DBC65D4479A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2989" uniqueCount="869">
   <si>
     <r>
       <t xml:space="preserve"># Hardware: </t>
@@ -1952,6 +1952,702 @@
     <t>c042c322-a246-4dfb-90b2-d3aa9c9f4008</t>
   </si>
   <si>
+    <t>46bd1d79-4398-4fce-a813-9ee86606f042</t>
+  </si>
+  <si>
+    <t>5378e051-1229-45e0-8f00-eb749937dc8d</t>
+  </si>
+  <si>
+    <t>f0472532-806e-4c62-a000-51ff649a077a</t>
+  </si>
+  <si>
+    <t>ceae880d-9f56-42f4-8920-acb53ceabcbb</t>
+  </si>
+  <si>
+    <t>b479cf92-0457-4927-af7a-4be513649b99</t>
+  </si>
+  <si>
+    <t>5814ae50-54e1-468b-b2a1-f322402e35f5</t>
+  </si>
+  <si>
+    <t>2bf7ced7-5894-4ad1-859d-8be50dd79c8c</t>
+  </si>
+  <si>
+    <t>392a3e9a-c54f-46a1-8660-f8e02c21322b</t>
+  </si>
+  <si>
+    <t>78dc7167-ece8-4a73-9ed9-24ddaeb3a96d</t>
+  </si>
+  <si>
+    <t>3324a4be-d988-40ba-9b35-0a7f94f7814c</t>
+  </si>
+  <si>
+    <t>e9555ed2-30ce-4dd6-ad50-69af9f4e3d69</t>
+  </si>
+  <si>
+    <t>95196a40-0867-44ac-8261-1e13ca6af62d</t>
+  </si>
+  <si>
+    <t>6e058ef2-69b6-4750-9945-2a1e94463d9d</t>
+  </si>
+  <si>
+    <t>8e34d482-35e0-4061-9d51-c9dd53588253</t>
+  </si>
+  <si>
+    <t>b482e1f8-2f8e-453b-971c-bc44a9d2b751</t>
+  </si>
+  <si>
+    <t>7397b2b1-2556-4f85-8c17-e39057a2fe0c</t>
+  </si>
+  <si>
+    <t>96e91a25-132f-44a1-8159-a1cc765da3be</t>
+  </si>
+  <si>
+    <t>5c2bd481-2e1c-485e-afed-b5e684b5c100</t>
+  </si>
+  <si>
+    <t>47f029c8-a785-4397-ace6-26c534484e8d</t>
+  </si>
+  <si>
+    <t>e7c19662-46c2-478d-ab76-64a7c8724bae</t>
+  </si>
+  <si>
+    <t>9e53e308-807b-44ab-a6bb-ad1325beadb9</t>
+  </si>
+  <si>
+    <t>fdf10c88-1ee2-4679-a8a8-2be2b99e5245</t>
+  </si>
+  <si>
+    <t>cbbc5633-f87d-4b87-9320-6da90469779e</t>
+  </si>
+  <si>
+    <t>eca6973c-ab32-4155-80cb-c4ce76e1ee63</t>
+  </si>
+  <si>
+    <t>380d6cab-4747-41bf-b378-e2cb0664263c</t>
+  </si>
+  <si>
+    <t>4509be58-09a4-43a4-824c-4ae377cc5268</t>
+  </si>
+  <si>
+    <t>a5eb7c28-fdf5-498e-9b51-0b5a5d3c9b26</t>
+  </si>
+  <si>
+    <t>882286a5-cd64-4e8e-9ef5-af626a15a246</t>
+  </si>
+  <si>
+    <t>88be942b-dffc-4529-b79f-aff792572f73</t>
+  </si>
+  <si>
+    <t>784a052b-cf02-4849-81e8-f796a47c2875</t>
+  </si>
+  <si>
+    <t>ee7b8ce6-f6bb-4023-81ae-3c91db0f0bf7</t>
+  </si>
+  <si>
+    <t>892ba149-cea0-411d-858a-0ce30c58c3a3</t>
+  </si>
+  <si>
+    <t>410bca04-239f-4957-b0db-4417cf1abaf8</t>
+  </si>
+  <si>
+    <t>2187fbb2-e33a-439b-ba9d-de765be65551</t>
+  </si>
+  <si>
+    <t>fd748e19-92d8-45bc-ae70-79c7bdb32202</t>
+  </si>
+  <si>
+    <t>d2f2952c-c2cd-4f36-8230-908564288ca1</t>
+  </si>
+  <si>
+    <t>2eed5d31-1d4c-450f-b133-ca5d45c7f521</t>
+  </si>
+  <si>
+    <t>59f0cd19-4cc2-4453-a5b2-542589d48b8f</t>
+  </si>
+  <si>
+    <t>befb6c5e-da6d-4497-991b-1dc250c4c0c6</t>
+  </si>
+  <si>
+    <t>dabd42bb-bad2-4d6f-bb26-41936f114aa9</t>
+  </si>
+  <si>
+    <t>9c639501-17b3-446a-9078-3b13b0b791b2</t>
+  </si>
+  <si>
+    <t>e3347ebd-b772-4d8e-9b37-173cba1503d2</t>
+  </si>
+  <si>
+    <t>3c1675c8-5e16-411e-ad64-3414b32abfb6</t>
+  </si>
+  <si>
+    <t>ecdd30e9-2655-41b7-8670-7223a35db123</t>
+  </si>
+  <si>
+    <t>88f4f6d9-dcbf-4d0d-ba11-8ab3f6e056ea</t>
+  </si>
+  <si>
+    <t>b5a3f0b1-06ed-4c6d-b0e5-10b0ed6f974c</t>
+  </si>
+  <si>
+    <t>6e0f49b5-9667-457b-b792-6a6cf46bf4a3</t>
+  </si>
+  <si>
+    <t>540e143b-1b28-403c-8db9-bf0081dc7e71</t>
+  </si>
+  <si>
+    <t>8810c6b1-3e40-47b0-b424-0095147e1c2e</t>
+  </si>
+  <si>
+    <t>c9417ef1-d902-406a-9c4c-5abd643bdcdd</t>
+  </si>
+  <si>
+    <t>bb444739-fce9-4e09-a86c-8fee1e3948b8</t>
+  </si>
+  <si>
+    <t>e4d26f1a-0dc2-4d91-a8b6-80305ecb90f4</t>
+  </si>
+  <si>
+    <t>818b4c29-96fc-42f9-9f66-fb9e7810bf99</t>
+  </si>
+  <si>
+    <t>819472b3-c361-4d0d-b072-32a46f8ad8ea</t>
+  </si>
+  <si>
+    <t>77924f1e-add7-466d-b1f4-4be5df6e254c</t>
+  </si>
+  <si>
+    <t>21caf008-231e-4cdd-8f8b-fc9dc0eb01de</t>
+  </si>
+  <si>
+    <t>b4c83ffa-0a0f-4088-b791-adbc72586283</t>
+  </si>
+  <si>
+    <t>25aac08e-b625-4bd4-9f19-d075e372d5a5</t>
+  </si>
+  <si>
+    <t>3aa5e643-29aa-4ce9-ba99-00f94a5a1869</t>
+  </si>
+  <si>
+    <t>52789f7f-8e9a-44ba-8207-55a3bbe12c91</t>
+  </si>
+  <si>
+    <t>d3647186-6faa-48fa-bec2-545bbd696935</t>
+  </si>
+  <si>
+    <t>89a959eb-022d-4830-b410-4f2316961966</t>
+  </si>
+  <si>
+    <t>b69a1572-747c-48ab-900e-31a86eb7731b</t>
+  </si>
+  <si>
+    <t>78e250ea-0e74-41be-8592-9ec9b9540f75</t>
+  </si>
+  <si>
+    <t>4ba09812-7f97-474b-a407-a03b449aeee8</t>
+  </si>
+  <si>
+    <t>62edb7b0-d499-4c01-a189-07b7834f3784</t>
+  </si>
+  <si>
+    <t>8a422a5b-038f-4451-b0d6-6c343f453a1f</t>
+  </si>
+  <si>
+    <t>999ee006-a5e1-4861-b909-04cafc583d0d</t>
+  </si>
+  <si>
+    <t>73634a09-82d5-4dab-91ff-0fce620ac22b</t>
+  </si>
+  <si>
+    <t>5c9aace0-89c9-4a2e-a022-08f828779d46</t>
+  </si>
+  <si>
+    <t>0ccaf546-d95b-4659-beb6-553540f3c41b</t>
+  </si>
+  <si>
+    <t>f3952754-cb9c-47c7-8a4a-6dcadaa33270</t>
+  </si>
+  <si>
+    <t>c7a1f54f-7e1f-4b2f-b908-6a1f273415cb</t>
+  </si>
+  <si>
+    <t>2faf43d4-f487-4210-9735-9f4ee7b1c717</t>
+  </si>
+  <si>
+    <t>4832fb28-83af-4bdd-ae9b-85d300653b91</t>
+  </si>
+  <si>
+    <t>b70e8f77-9599-44a0-ade6-e333c44742f8</t>
+  </si>
+  <si>
+    <t>d85f3dc2-218d-471f-a323-02260069e933</t>
+  </si>
+  <si>
+    <t>fc9691fb-0a4d-4ad9-a31f-ac6601be6008</t>
+  </si>
+  <si>
+    <t>3271b402-6925-4c43-aac9-f6a3234d4ce8</t>
+  </si>
+  <si>
+    <t>916a7d5d-63cb-457b-b4a3-85c0b7d1c824</t>
+  </si>
+  <si>
+    <t>b9e8a1a0-25e2-4dac-b22e-becf7e64a5dc</t>
+  </si>
+  <si>
+    <t>3ecdcdb1-2cc6-4bf9-8654-aae243be5c68</t>
+  </si>
+  <si>
+    <t>e52f4818-2f96-42b7-be7b-6b6f4ddce6a9</t>
+  </si>
+  <si>
+    <t>b7c8bad6-7eb3-4404-ac5d-11b5167319c7</t>
+  </si>
+  <si>
+    <t>43bf1f6b-6823-447f-813a-1ffa9259e799</t>
+  </si>
+  <si>
+    <t>95a2e98e-50a3-4d23-8035-a6de11c55881</t>
+  </si>
+  <si>
+    <t>accd7127-b34a-478f-ae7e-2664dfcdbba3</t>
+  </si>
+  <si>
+    <t>1bb337c9-4476-4419-9ab0-a5a011a82e92</t>
+  </si>
+  <si>
+    <t>3abf03c0-b5c5-4641-a510-e25eb5a7b856</t>
+  </si>
+  <si>
+    <t>38fecd2c-8581-4f93-a4f5-c1cc3fbd6c44</t>
+  </si>
+  <si>
+    <t>f046bcaf-12f1-4a8d-b515-254bfb43252d</t>
+  </si>
+  <si>
+    <t>fb3e0e8d-390a-408a-9c7b-c89718031bdf</t>
+  </si>
+  <si>
+    <t>b5bb7a2a-5615-4405-bf1f-5830f08e0546</t>
+  </si>
+  <si>
+    <t>ca96c9f7-b95b-4acf-82c9-75df7c339b8d</t>
+  </si>
+  <si>
+    <t>b9226424-5f38-40d9-9e7d-cefd8b03d458</t>
+  </si>
+  <si>
+    <t>85cfe389-182e-4a04-a7be-2468b515ed92</t>
+  </si>
+  <si>
+    <t>cf005af9-5caa-4010-84e9-9d97896939e8</t>
+  </si>
+  <si>
+    <t>8bc3ac18-5c83-49b4-8718-4b683f19ae9f</t>
+  </si>
+  <si>
+    <t>08ea3659-25d6-4145-aa9e-b4c4e34be849</t>
+  </si>
+  <si>
+    <t>7bcfc337-ab4b-4b6f-8f17-3c000e97553b</t>
+  </si>
+  <si>
+    <t>30f61096-0db8-4896-a6c0-47081fbab9da</t>
+  </si>
+  <si>
+    <t>3dce181f-2216-47a2-b239-e8682f6c7845</t>
+  </si>
+  <si>
+    <t>296b202f-9886-496f-a267-f5ab8df3650d</t>
+  </si>
+  <si>
+    <t>cf51c29b-3377-43a4-8229-1c7bf3f98dd5</t>
+  </si>
+  <si>
+    <t>112338a7-a98d-42ee-8b9e-01f604f2046d</t>
+  </si>
+  <si>
+    <t>d7bfb56d-274b-485e-a7bf-189ebd822f64</t>
+  </si>
+  <si>
+    <t>80c4d9d4-1f36-4a76-b686-5c8defe41510</t>
+  </si>
+  <si>
+    <t>e3a3388b-29d2-4aca-b953-f6fd9345fc67</t>
+  </si>
+  <si>
+    <t>a9ff400b-a30c-4ba4-97ae-43e3fcdcbffb</t>
+  </si>
+  <si>
+    <t>30344395-147d-4090-abf0-e47c713b1d81</t>
+  </si>
+  <si>
+    <t>1db1e374-a543-443c-9977-759761ce4c5e</t>
+  </si>
+  <si>
+    <t>1647f6c9-c922-4049-9d78-1d9b33797525</t>
+  </si>
+  <si>
+    <t>30db59ba-8616-473b-872e-e1c54be88efa</t>
+  </si>
+  <si>
+    <t>d298bacf-edda-47bd-b2ba-6823955417c2</t>
+  </si>
+  <si>
+    <t>63760865-4bee-4431-9e29-f2661fa46007</t>
+  </si>
+  <si>
+    <t>605bec3d-86e6-4ae0-ad83-826c93c5ead1</t>
+  </si>
+  <si>
+    <t>82a929e5-9a44-4412-bb27-4b1eac130c61</t>
+  </si>
+  <si>
+    <t>2efe631c-a748-4e4b-b954-7e870a90e20c</t>
+  </si>
+  <si>
+    <t>137d5adf-e535-4df4-ac78-6ac5b0a498a7</t>
+  </si>
+  <si>
+    <t>e41237c7-0081-4150-930f-f668fe26be29</t>
+  </si>
+  <si>
+    <t>ee556fe0-b472-4959-bd1c-7ec700842ef5</t>
+  </si>
+  <si>
+    <t>8551351a-5a75-43a9-a194-c02c1cc69ffc</t>
+  </si>
+  <si>
+    <t>24ce8e4b-a575-4cdb-ae61-f34c68160efc</t>
+  </si>
+  <si>
+    <t>8a8d421f-bf8b-4192-80af-0d43b7787cbe</t>
+  </si>
+  <si>
+    <t>a8cc4705-2efe-4548-9dd9-5b0d1139edfa</t>
+  </si>
+  <si>
+    <t>603aa9d3-6ca0-46fc-b986-502ea8acc908</t>
+  </si>
+  <si>
+    <t>b623abae-9f91-4ff3-9591-3b6a4b023fba</t>
+  </si>
+  <si>
+    <t>968f2c4d-0d6d-47a6-acff-5cfc06f88f0a</t>
+  </si>
+  <si>
+    <t>a9c1bd64-369f-4c7c-970c-af21046e7be8</t>
+  </si>
+  <si>
+    <t>a9b02433-55c0-463f-9b32-33136b5629b8</t>
+  </si>
+  <si>
+    <t>9a738b1e-9e3d-4e36-af63-3aa244b29d87</t>
+  </si>
+  <si>
+    <t>497f613f-d254-4394-8dfa-c63d4ec48d00</t>
+  </si>
+  <si>
+    <t>26c5bb28-e77f-4139-ba30-35a8bd1e227f</t>
+  </si>
+  <si>
+    <t>7eb7d903-b089-495b-907f-c1f043d0a6cb</t>
+  </si>
+  <si>
+    <t>3c35d770-50b0-48b6-8d8e-e69c69198abf</t>
+  </si>
+  <si>
+    <t>feec19b3-6cb2-41b2-9bce-7c4b68bd1c25</t>
+  </si>
+  <si>
+    <t>51dbaea4-7f60-4e62-9ac3-43e8161b4802</t>
+  </si>
+  <si>
+    <t>38736d81-584a-498f-8419-22db6fd1f78a</t>
+  </si>
+  <si>
+    <t>beb7c9a3-a3f1-42af-bb10-15fe5cf7589c</t>
+  </si>
+  <si>
+    <t>78dbc454-b4ad-41b0-bc73-5e0de0474869</t>
+  </si>
+  <si>
+    <t>feffcba7-9d32-4267-8142-df9cac79a221</t>
+  </si>
+  <si>
+    <t>1ff8c3c6-e9a4-4236-ae9b-60b2e70eef8e</t>
+  </si>
+  <si>
+    <t>4cd9dbc7-ca54-4e47-a90d-5b7de006389c</t>
+  </si>
+  <si>
+    <t>80f75e15-a436-41cc-a492-42409bd09dfe</t>
+  </si>
+  <si>
+    <t>3bd19453-f894-4df6-b98d-57a70e9704a0</t>
+  </si>
+  <si>
+    <t>19a30776-efb8-4b0f-9688-5495eabbd5a8</t>
+  </si>
+  <si>
+    <t>cff6dee6-c17f-452f-8fd1-375cd00859ed</t>
+  </si>
+  <si>
+    <t>da27f3dd-eeb3-4768-90ac-a137f3997628</t>
+  </si>
+  <si>
+    <t>dc8c4e5f-2320-419e-9e8b-bc672457f64a</t>
+  </si>
+  <si>
+    <t>b61a4f8d-9f7c-4a5a-91af-231341743367</t>
+  </si>
+  <si>
+    <t>aa819db9-1fe6-48d0-bef6-8adc9dcf27fa</t>
+  </si>
+  <si>
+    <t>d0e9f75a-c208-4dbd-a50c-4130b46d3f88</t>
+  </si>
+  <si>
+    <t>dcc5a8a4-4d58-4f49-a097-5e0b8b6efabe</t>
+  </si>
+  <si>
+    <t>5175ab54-8ce9-4286-b884-0dbeed92260e</t>
+  </si>
+  <si>
+    <t>fb2a3721-2596-457b-ba12-cd00178da9e7</t>
+  </si>
+  <si>
+    <t>6b718e72-09be-49de-95ce-0a73a5d5fdb8</t>
+  </si>
+  <si>
+    <t>897e9de7-8bef-418a-8390-53846ff24cd6</t>
+  </si>
+  <si>
+    <t>3705a259-42cc-4eda-bb88-3d0f247dfb4e</t>
+  </si>
+  <si>
+    <t>493c1423-6789-4cf5-bac2-bae71dc686b4</t>
+  </si>
+  <si>
+    <t>0e396489-579f-41c3-b18f-47d79cc44244</t>
+  </si>
+  <si>
+    <t>543e03a2-d476-484d-9ff6-1ecdeb1e3107</t>
+  </si>
+  <si>
+    <t>8a9b36e5-789a-40ee-b8d8-61e4a553f722</t>
+  </si>
+  <si>
+    <t>48681054-aa0f-47f4-950c-84ed699a24fa</t>
+  </si>
+  <si>
+    <t>7de282d6-6309-4fb3-8dad-505d745c312a</t>
+  </si>
+  <si>
+    <t>bc94d0f4-6f80-46d1-8a4a-03e42ae37e67</t>
+  </si>
+  <si>
+    <t>79ccfd74-0319-410f-8c7f-9baf9fa1232d</t>
+  </si>
+  <si>
+    <t>036ec42f-6c95-4d81-a35c-ade53947c34a</t>
+  </si>
+  <si>
+    <t>0f7b6da8-415d-40bd-84bf-7b455197ebdf</t>
+  </si>
+  <si>
+    <t>fc1d64ff-f77c-40d9-94c9-f0bb7e886737</t>
+  </si>
+  <si>
+    <t>8c4796b5-3f5c-4733-8201-78d9aa31baa4</t>
+  </si>
+  <si>
+    <t>72a0e825-104b-4be8-8f8d-0353825d2545</t>
+  </si>
+  <si>
+    <t>ab864e2d-accf-4514-9898-7b618c63e9fc</t>
+  </si>
+  <si>
+    <t>99efe2b5-366d-41d5-bd50-cc8c89172454</t>
+  </si>
+  <si>
+    <t>11e24f28-a53e-43a7-93e1-a21aab719045</t>
+  </si>
+  <si>
+    <t>72794a34-2128-4cb8-b9c4-a73c8745d64e</t>
+  </si>
+  <si>
+    <t>2f2096bb-cb30-4429-b00f-82da78ca940d</t>
+  </si>
+  <si>
+    <t>2250b992-9d6a-4c80-8259-50e8485a363d</t>
+  </si>
+  <si>
+    <t>ba377f88-c272-4653-b088-414dfbddaa27</t>
+  </si>
+  <si>
+    <t>16aa934c-6564-4a3e-bf55-477bd1ed3a68</t>
+  </si>
+  <si>
+    <t>36b4d0ab-497c-4f61-9b8f-a068fdde642c</t>
+  </si>
+  <si>
+    <t>47a45f4e-cc69-4781-8efb-f0769e59ac4b</t>
+  </si>
+  <si>
+    <t>7027d585-5012-43e8-ab09-063650ac845d</t>
+  </si>
+  <si>
+    <t>c030328b-64c9-4507-a610-f2691dd79804</t>
+  </si>
+  <si>
+    <t>9b417d1d-07f2-4dfb-ac96-d02c0974f394</t>
+  </si>
+  <si>
+    <t>339f78ae-ab73-43c7-8b29-8314fe185b24</t>
+  </si>
+  <si>
+    <t>8bc6c1f4-0f36-46fe-863e-66c7fcbd96e7</t>
+  </si>
+  <si>
+    <t>246f5066-497a-4418-9aa3-f4188f2c89d9</t>
+  </si>
+  <si>
+    <t>af55b0dd-712f-4e2c-a05f-b3ec606aa811</t>
+  </si>
+  <si>
+    <t>6aad7c3a-c50e-4381-993a-02c7e340bad6</t>
+  </si>
+  <si>
+    <t>0b46e83c-b8b0-49d1-81c4-6e75aafc5c4d</t>
+  </si>
+  <si>
+    <t>7d4e6c95-6817-427a-a34d-70ecc005403c</t>
+  </si>
+  <si>
+    <t>bf3eeb2f-6905-42e2-8a84-8bfdd849c230</t>
+  </si>
+  <si>
+    <t>9e811c4f-16b8-4892-a3b9-329ffa11ad5a</t>
+  </si>
+  <si>
+    <t>e0e7e059-4a63-47b0-b056-628a1d8dff5a</t>
+  </si>
+  <si>
+    <t>3aae4f08-a9b6-45c0-91ed-3d119337cfaa</t>
+  </si>
+  <si>
+    <t>55968f05-af8b-4517-9feb-ed1b89eef2d3</t>
+  </si>
+  <si>
+    <t>6f92a3aa-95a9-4e4b-9fbb-bbe781591b47</t>
+  </si>
+  <si>
+    <t>f689740a-551a-45e7-822f-418eb3da6b00</t>
+  </si>
+  <si>
+    <t>e9800206-8524-4371-8a30-f900919ce25b</t>
+  </si>
+  <si>
+    <t>5f52cbb8-bb8d-46cf-9fa7-719978353711</t>
+  </si>
+  <si>
+    <t>08101094-8561-4275-8ad8-932ec134ac66</t>
+  </si>
+  <si>
+    <t>9bd6dc80-4d02-4758-8b2d-009576906cf3</t>
+  </si>
+  <si>
+    <t>e7567fb1-5401-47d9-8cbd-f371f57ef72a</t>
+  </si>
+  <si>
+    <t>4c86547c-be31-4c09-84b1-4750d0128200</t>
+  </si>
+  <si>
+    <t>7d7be2a6-a8a7-4884-a5e8-1bbe5a1a5783</t>
+  </si>
+  <si>
+    <t>ba39552a-6651-4804-b8ed-b215ccda123e</t>
+  </si>
+  <si>
+    <t>26f629fd-4969-4aa8-9324-ac4a37568160</t>
+  </si>
+  <si>
+    <t>da7b6560-09b0-4e7f-9a15-7e63844a242e</t>
+  </si>
+  <si>
+    <t>97446a2b-266c-4e17-aa5e-234e8e3e252b</t>
+  </si>
+  <si>
+    <t>bf05e09f-0de6-4343-bb82-a25331b06f4f</t>
+  </si>
+  <si>
+    <t>0e00edcf-fe49-489a-8f29-bced7aa6ae09</t>
+  </si>
+  <si>
+    <t>6f2477cc-efe7-4dc2-84db-2deb37cb7da7</t>
+  </si>
+  <si>
+    <t>f7323fa7-e9c3-4a83-89d0-ac9d317b1efb</t>
+  </si>
+  <si>
+    <t>194c40f1-37d8-43f3-8ed7-0113c35ba40d</t>
+  </si>
+  <si>
+    <t>703fbd73-57b2-403c-a8e6-39df9b258dfd</t>
+  </si>
+  <si>
+    <t>15d10fc1-dddd-4c98-b9b6-c9a0f39550e7</t>
+  </si>
+  <si>
+    <t>d482f3bb-9c33-4046-a36b-3c7ee6ef1663</t>
+  </si>
+  <si>
+    <t>62479591-94d2-4ef7-a834-cae87f381383</t>
+  </si>
+  <si>
+    <t>ca86e696-bd55-414c-b38f-fee5e034a3e9</t>
+  </si>
+  <si>
+    <t>e02b1b3c-7247-41a6-9ddb-166952df5d3d</t>
+  </si>
+  <si>
+    <t>b107f0ed-6116-43d7-807c-c7e43065be2f</t>
+  </si>
+  <si>
+    <t>6d568953-050f-4bea-b803-4b786956c5ae</t>
+  </si>
+  <si>
+    <t>dfb92c50-c40a-4168-941b-c87af3270f95</t>
+  </si>
+  <si>
+    <t>741b6837-5d16-4c96-8f17-2ebedbd493c7</t>
+  </si>
+  <si>
+    <t>f4b57015-ecd3-4656-a441-17a064320194</t>
+  </si>
+  <si>
+    <t>3db28621-e212-4bef-a1a6-485f0cd5c6d0</t>
+  </si>
+  <si>
+    <t>ce918d78-4a5b-4e61-9c26-c354b03edd0c</t>
+  </si>
+  <si>
+    <t>02306e58-4dca-4124-8d6d-c25928ec0980</t>
+  </si>
+  <si>
+    <t>f81c05ee-a3fa-4f88-b77f-87f315e6ad67</t>
+  </si>
+  <si>
+    <t>ZX Spectrum/Spectrum+ Service Manual</t>
+  </si>
+  <si>
+    <t>ZX Spectrum/Shared files/Board local files/ZX-Spectrum-Service-Manual.pdf</t>
+  </si>
+  <si>
+    <t>5b1f5209-250a-4414-8434-126bb53e2fb2</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -1963,704 +2659,35 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2026-May-16</t>
+      <t>2026-September-9</t>
     </r>
   </si>
   <si>
-    <t>46bd1d79-4398-4fce-a813-9ee86606f042</t>
-  </si>
-  <si>
-    <t>5378e051-1229-45e0-8f00-eb749937dc8d</t>
-  </si>
-  <si>
-    <t>f0472532-806e-4c62-a000-51ff649a077a</t>
-  </si>
-  <si>
-    <t>ceae880d-9f56-42f4-8920-acb53ceabcbb</t>
-  </si>
-  <si>
-    <t>b479cf92-0457-4927-af7a-4be513649b99</t>
-  </si>
-  <si>
-    <t>5814ae50-54e1-468b-b2a1-f322402e35f5</t>
-  </si>
-  <si>
-    <t>2bf7ced7-5894-4ad1-859d-8be50dd79c8c</t>
-  </si>
-  <si>
-    <t>392a3e9a-c54f-46a1-8660-f8e02c21322b</t>
-  </si>
-  <si>
-    <t>78dc7167-ece8-4a73-9ed9-24ddaeb3a96d</t>
-  </si>
-  <si>
-    <t>3324a4be-d988-40ba-9b35-0a7f94f7814c</t>
-  </si>
-  <si>
-    <t>e9555ed2-30ce-4dd6-ad50-69af9f4e3d69</t>
-  </si>
-  <si>
-    <t>95196a40-0867-44ac-8261-1e13ca6af62d</t>
-  </si>
-  <si>
-    <t>6e058ef2-69b6-4750-9945-2a1e94463d9d</t>
-  </si>
-  <si>
-    <t>8e34d482-35e0-4061-9d51-c9dd53588253</t>
-  </si>
-  <si>
-    <t>b482e1f8-2f8e-453b-971c-bc44a9d2b751</t>
-  </si>
-  <si>
-    <t>7397b2b1-2556-4f85-8c17-e39057a2fe0c</t>
-  </si>
-  <si>
-    <t>96e91a25-132f-44a1-8159-a1cc765da3be</t>
-  </si>
-  <si>
-    <t>5c2bd481-2e1c-485e-afed-b5e684b5c100</t>
-  </si>
-  <si>
-    <t>47f029c8-a785-4397-ace6-26c534484e8d</t>
-  </si>
-  <si>
-    <t>e7c19662-46c2-478d-ab76-64a7c8724bae</t>
-  </si>
-  <si>
-    <t>9e53e308-807b-44ab-a6bb-ad1325beadb9</t>
-  </si>
-  <si>
-    <t>fdf10c88-1ee2-4679-a8a8-2be2b99e5245</t>
-  </si>
-  <si>
-    <t>cbbc5633-f87d-4b87-9320-6da90469779e</t>
-  </si>
-  <si>
-    <t>eca6973c-ab32-4155-80cb-c4ce76e1ee63</t>
-  </si>
-  <si>
-    <t>380d6cab-4747-41bf-b378-e2cb0664263c</t>
-  </si>
-  <si>
-    <t>4509be58-09a4-43a4-824c-4ae377cc5268</t>
-  </si>
-  <si>
-    <t>a5eb7c28-fdf5-498e-9b51-0b5a5d3c9b26</t>
-  </si>
-  <si>
-    <t>882286a5-cd64-4e8e-9ef5-af626a15a246</t>
-  </si>
-  <si>
-    <t>88be942b-dffc-4529-b79f-aff792572f73</t>
-  </si>
-  <si>
-    <t>784a052b-cf02-4849-81e8-f796a47c2875</t>
-  </si>
-  <si>
-    <t>ee7b8ce6-f6bb-4023-81ae-3c91db0f0bf7</t>
-  </si>
-  <si>
-    <t>892ba149-cea0-411d-858a-0ce30c58c3a3</t>
-  </si>
-  <si>
-    <t>410bca04-239f-4957-b0db-4417cf1abaf8</t>
-  </si>
-  <si>
-    <t>2187fbb2-e33a-439b-ba9d-de765be65551</t>
-  </si>
-  <si>
-    <t>fd748e19-92d8-45bc-ae70-79c7bdb32202</t>
-  </si>
-  <si>
-    <t>d2f2952c-c2cd-4f36-8230-908564288ca1</t>
-  </si>
-  <si>
-    <t>2eed5d31-1d4c-450f-b133-ca5d45c7f521</t>
-  </si>
-  <si>
-    <t>59f0cd19-4cc2-4453-a5b2-542589d48b8f</t>
-  </si>
-  <si>
-    <t>befb6c5e-da6d-4497-991b-1dc250c4c0c6</t>
-  </si>
-  <si>
-    <t>dabd42bb-bad2-4d6f-bb26-41936f114aa9</t>
-  </si>
-  <si>
-    <t>9c639501-17b3-446a-9078-3b13b0b791b2</t>
-  </si>
-  <si>
-    <t>e3347ebd-b772-4d8e-9b37-173cba1503d2</t>
-  </si>
-  <si>
-    <t>3c1675c8-5e16-411e-ad64-3414b32abfb6</t>
-  </si>
-  <si>
-    <t>ecdd30e9-2655-41b7-8670-7223a35db123</t>
-  </si>
-  <si>
-    <t>88f4f6d9-dcbf-4d0d-ba11-8ab3f6e056ea</t>
-  </si>
-  <si>
-    <t>b5a3f0b1-06ed-4c6d-b0e5-10b0ed6f974c</t>
-  </si>
-  <si>
-    <t>6e0f49b5-9667-457b-b792-6a6cf46bf4a3</t>
-  </si>
-  <si>
-    <t>540e143b-1b28-403c-8db9-bf0081dc7e71</t>
-  </si>
-  <si>
-    <t>8810c6b1-3e40-47b0-b424-0095147e1c2e</t>
-  </si>
-  <si>
-    <t>c9417ef1-d902-406a-9c4c-5abd643bdcdd</t>
-  </si>
-  <si>
-    <t>bb444739-fce9-4e09-a86c-8fee1e3948b8</t>
-  </si>
-  <si>
-    <t>e4d26f1a-0dc2-4d91-a8b6-80305ecb90f4</t>
-  </si>
-  <si>
-    <t>818b4c29-96fc-42f9-9f66-fb9e7810bf99</t>
-  </si>
-  <si>
-    <t>819472b3-c361-4d0d-b072-32a46f8ad8ea</t>
-  </si>
-  <si>
-    <t>77924f1e-add7-466d-b1f4-4be5df6e254c</t>
-  </si>
-  <si>
-    <t>21caf008-231e-4cdd-8f8b-fc9dc0eb01de</t>
-  </si>
-  <si>
-    <t>b4c83ffa-0a0f-4088-b791-adbc72586283</t>
-  </si>
-  <si>
-    <t>25aac08e-b625-4bd4-9f19-d075e372d5a5</t>
-  </si>
-  <si>
-    <t>3aa5e643-29aa-4ce9-ba99-00f94a5a1869</t>
-  </si>
-  <si>
-    <t>52789f7f-8e9a-44ba-8207-55a3bbe12c91</t>
-  </si>
-  <si>
-    <t>d3647186-6faa-48fa-bec2-545bbd696935</t>
-  </si>
-  <si>
-    <t>89a959eb-022d-4830-b410-4f2316961966</t>
-  </si>
-  <si>
-    <t>b69a1572-747c-48ab-900e-31a86eb7731b</t>
-  </si>
-  <si>
-    <t>78e250ea-0e74-41be-8592-9ec9b9540f75</t>
-  </si>
-  <si>
-    <t>4ba09812-7f97-474b-a407-a03b449aeee8</t>
-  </si>
-  <si>
-    <t>62edb7b0-d499-4c01-a189-07b7834f3784</t>
-  </si>
-  <si>
-    <t>8a422a5b-038f-4451-b0d6-6c343f453a1f</t>
-  </si>
-  <si>
-    <t>999ee006-a5e1-4861-b909-04cafc583d0d</t>
-  </si>
-  <si>
-    <t>73634a09-82d5-4dab-91ff-0fce620ac22b</t>
-  </si>
-  <si>
-    <t>5c9aace0-89c9-4a2e-a022-08f828779d46</t>
-  </si>
-  <si>
-    <t>0ccaf546-d95b-4659-beb6-553540f3c41b</t>
-  </si>
-  <si>
-    <t>f3952754-cb9c-47c7-8a4a-6dcadaa33270</t>
-  </si>
-  <si>
-    <t>c7a1f54f-7e1f-4b2f-b908-6a1f273415cb</t>
-  </si>
-  <si>
-    <t>2faf43d4-f487-4210-9735-9f4ee7b1c717</t>
-  </si>
-  <si>
-    <t>4832fb28-83af-4bdd-ae9b-85d300653b91</t>
-  </si>
-  <si>
-    <t>b70e8f77-9599-44a0-ade6-e333c44742f8</t>
-  </si>
-  <si>
-    <t>d85f3dc2-218d-471f-a323-02260069e933</t>
-  </si>
-  <si>
-    <t>fc9691fb-0a4d-4ad9-a31f-ac6601be6008</t>
-  </si>
-  <si>
-    <t>3271b402-6925-4c43-aac9-f6a3234d4ce8</t>
-  </si>
-  <si>
-    <t>916a7d5d-63cb-457b-b4a3-85c0b7d1c824</t>
-  </si>
-  <si>
-    <t>b9e8a1a0-25e2-4dac-b22e-becf7e64a5dc</t>
-  </si>
-  <si>
-    <t>3ecdcdb1-2cc6-4bf9-8654-aae243be5c68</t>
-  </si>
-  <si>
-    <t>e52f4818-2f96-42b7-be7b-6b6f4ddce6a9</t>
-  </si>
-  <si>
-    <t>b7c8bad6-7eb3-4404-ac5d-11b5167319c7</t>
-  </si>
-  <si>
-    <t>43bf1f6b-6823-447f-813a-1ffa9259e799</t>
-  </si>
-  <si>
-    <t>95a2e98e-50a3-4d23-8035-a6de11c55881</t>
-  </si>
-  <si>
-    <t>accd7127-b34a-478f-ae7e-2664dfcdbba3</t>
-  </si>
-  <si>
-    <t>1bb337c9-4476-4419-9ab0-a5a011a82e92</t>
-  </si>
-  <si>
-    <t>3abf03c0-b5c5-4641-a510-e25eb5a7b856</t>
-  </si>
-  <si>
-    <t>38fecd2c-8581-4f93-a4f5-c1cc3fbd6c44</t>
-  </si>
-  <si>
-    <t>f046bcaf-12f1-4a8d-b515-254bfb43252d</t>
-  </si>
-  <si>
-    <t>fb3e0e8d-390a-408a-9c7b-c89718031bdf</t>
-  </si>
-  <si>
-    <t>b5bb7a2a-5615-4405-bf1f-5830f08e0546</t>
-  </si>
-  <si>
-    <t>ca96c9f7-b95b-4acf-82c9-75df7c339b8d</t>
-  </si>
-  <si>
-    <t>b9226424-5f38-40d9-9e7d-cefd8b03d458</t>
-  </si>
-  <si>
-    <t>85cfe389-182e-4a04-a7be-2468b515ed92</t>
-  </si>
-  <si>
-    <t>cf005af9-5caa-4010-84e9-9d97896939e8</t>
-  </si>
-  <si>
-    <t>8bc3ac18-5c83-49b4-8718-4b683f19ae9f</t>
-  </si>
-  <si>
-    <t>08ea3659-25d6-4145-aa9e-b4c4e34be849</t>
-  </si>
-  <si>
-    <t>7bcfc337-ab4b-4b6f-8f17-3c000e97553b</t>
-  </si>
-  <si>
-    <t>30f61096-0db8-4896-a6c0-47081fbab9da</t>
-  </si>
-  <si>
-    <t>3dce181f-2216-47a2-b239-e8682f6c7845</t>
-  </si>
-  <si>
-    <t>296b202f-9886-496f-a267-f5ab8df3650d</t>
-  </si>
-  <si>
-    <t>cf51c29b-3377-43a4-8229-1c7bf3f98dd5</t>
-  </si>
-  <si>
-    <t>112338a7-a98d-42ee-8b9e-01f604f2046d</t>
-  </si>
-  <si>
-    <t>d7bfb56d-274b-485e-a7bf-189ebd822f64</t>
-  </si>
-  <si>
-    <t>80c4d9d4-1f36-4a76-b686-5c8defe41510</t>
-  </si>
-  <si>
-    <t>e3a3388b-29d2-4aca-b953-f6fd9345fc67</t>
-  </si>
-  <si>
-    <t>a9ff400b-a30c-4ba4-97ae-43e3fcdcbffb</t>
-  </si>
-  <si>
-    <t>30344395-147d-4090-abf0-e47c713b1d81</t>
-  </si>
-  <si>
-    <t>1db1e374-a543-443c-9977-759761ce4c5e</t>
-  </si>
-  <si>
-    <t>1647f6c9-c922-4049-9d78-1d9b33797525</t>
-  </si>
-  <si>
-    <t>30db59ba-8616-473b-872e-e1c54be88efa</t>
-  </si>
-  <si>
-    <t>d298bacf-edda-47bd-b2ba-6823955417c2</t>
-  </si>
-  <si>
-    <t>63760865-4bee-4431-9e29-f2661fa46007</t>
-  </si>
-  <si>
-    <t>605bec3d-86e6-4ae0-ad83-826c93c5ead1</t>
-  </si>
-  <si>
-    <t>82a929e5-9a44-4412-bb27-4b1eac130c61</t>
-  </si>
-  <si>
-    <t>2efe631c-a748-4e4b-b954-7e870a90e20c</t>
-  </si>
-  <si>
-    <t>137d5adf-e535-4df4-ac78-6ac5b0a498a7</t>
-  </si>
-  <si>
-    <t>e41237c7-0081-4150-930f-f668fe26be29</t>
-  </si>
-  <si>
-    <t>ee556fe0-b472-4959-bd1c-7ec700842ef5</t>
-  </si>
-  <si>
-    <t>8551351a-5a75-43a9-a194-c02c1cc69ffc</t>
-  </si>
-  <si>
-    <t>24ce8e4b-a575-4cdb-ae61-f34c68160efc</t>
-  </si>
-  <si>
-    <t>8a8d421f-bf8b-4192-80af-0d43b7787cbe</t>
-  </si>
-  <si>
-    <t>a8cc4705-2efe-4548-9dd9-5b0d1139edfa</t>
-  </si>
-  <si>
-    <t>603aa9d3-6ca0-46fc-b986-502ea8acc908</t>
-  </si>
-  <si>
-    <t>b623abae-9f91-4ff3-9591-3b6a4b023fba</t>
-  </si>
-  <si>
-    <t>968f2c4d-0d6d-47a6-acff-5cfc06f88f0a</t>
-  </si>
-  <si>
-    <t>a9c1bd64-369f-4c7c-970c-af21046e7be8</t>
-  </si>
-  <si>
-    <t>a9b02433-55c0-463f-9b32-33136b5629b8</t>
-  </si>
-  <si>
-    <t>9a738b1e-9e3d-4e36-af63-3aa244b29d87</t>
-  </si>
-  <si>
-    <t>497f613f-d254-4394-8dfa-c63d4ec48d00</t>
-  </si>
-  <si>
-    <t>26c5bb28-e77f-4139-ba30-35a8bd1e227f</t>
-  </si>
-  <si>
-    <t>7eb7d903-b089-495b-907f-c1f043d0a6cb</t>
-  </si>
-  <si>
-    <t>3c35d770-50b0-48b6-8d8e-e69c69198abf</t>
-  </si>
-  <si>
-    <t>feec19b3-6cb2-41b2-9bce-7c4b68bd1c25</t>
-  </si>
-  <si>
-    <t>51dbaea4-7f60-4e62-9ac3-43e8161b4802</t>
-  </si>
-  <si>
-    <t>38736d81-584a-498f-8419-22db6fd1f78a</t>
-  </si>
-  <si>
-    <t>beb7c9a3-a3f1-42af-bb10-15fe5cf7589c</t>
-  </si>
-  <si>
-    <t>78dbc454-b4ad-41b0-bc73-5e0de0474869</t>
-  </si>
-  <si>
-    <t>feffcba7-9d32-4267-8142-df9cac79a221</t>
-  </si>
-  <si>
-    <t>1ff8c3c6-e9a4-4236-ae9b-60b2e70eef8e</t>
-  </si>
-  <si>
-    <t>4cd9dbc7-ca54-4e47-a90d-5b7de006389c</t>
-  </si>
-  <si>
-    <t>80f75e15-a436-41cc-a492-42409bd09dfe</t>
-  </si>
-  <si>
-    <t>3bd19453-f894-4df6-b98d-57a70e9704a0</t>
-  </si>
-  <si>
-    <t>19a30776-efb8-4b0f-9688-5495eabbd5a8</t>
-  </si>
-  <si>
-    <t>cff6dee6-c17f-452f-8fd1-375cd00859ed</t>
-  </si>
-  <si>
-    <t>da27f3dd-eeb3-4768-90ac-a137f3997628</t>
-  </si>
-  <si>
-    <t>dc8c4e5f-2320-419e-9e8b-bc672457f64a</t>
-  </si>
-  <si>
-    <t>b61a4f8d-9f7c-4a5a-91af-231341743367</t>
-  </si>
-  <si>
-    <t>aa819db9-1fe6-48d0-bef6-8adc9dcf27fa</t>
-  </si>
-  <si>
-    <t>d0e9f75a-c208-4dbd-a50c-4130b46d3f88</t>
-  </si>
-  <si>
-    <t>dcc5a8a4-4d58-4f49-a097-5e0b8b6efabe</t>
-  </si>
-  <si>
-    <t>5175ab54-8ce9-4286-b884-0dbeed92260e</t>
-  </si>
-  <si>
-    <t>fb2a3721-2596-457b-ba12-cd00178da9e7</t>
-  </si>
-  <si>
-    <t>6b718e72-09be-49de-95ce-0a73a5d5fdb8</t>
-  </si>
-  <si>
-    <t>897e9de7-8bef-418a-8390-53846ff24cd6</t>
-  </si>
-  <si>
-    <t>3705a259-42cc-4eda-bb88-3d0f247dfb4e</t>
-  </si>
-  <si>
-    <t>493c1423-6789-4cf5-bac2-bae71dc686b4</t>
-  </si>
-  <si>
-    <t>0e396489-579f-41c3-b18f-47d79cc44244</t>
-  </si>
-  <si>
-    <t>543e03a2-d476-484d-9ff6-1ecdeb1e3107</t>
-  </si>
-  <si>
-    <t>8a9b36e5-789a-40ee-b8d8-61e4a553f722</t>
-  </si>
-  <si>
-    <t>48681054-aa0f-47f4-950c-84ed699a24fa</t>
-  </si>
-  <si>
-    <t>7de282d6-6309-4fb3-8dad-505d745c312a</t>
-  </si>
-  <si>
-    <t>bc94d0f4-6f80-46d1-8a4a-03e42ae37e67</t>
-  </si>
-  <si>
-    <t>79ccfd74-0319-410f-8c7f-9baf9fa1232d</t>
-  </si>
-  <si>
-    <t>036ec42f-6c95-4d81-a35c-ade53947c34a</t>
-  </si>
-  <si>
-    <t>0f7b6da8-415d-40bd-84bf-7b455197ebdf</t>
-  </si>
-  <si>
-    <t>fc1d64ff-f77c-40d9-94c9-f0bb7e886737</t>
-  </si>
-  <si>
-    <t>8c4796b5-3f5c-4733-8201-78d9aa31baa4</t>
-  </si>
-  <si>
-    <t>72a0e825-104b-4be8-8f8d-0353825d2545</t>
-  </si>
-  <si>
-    <t>ab864e2d-accf-4514-9898-7b618c63e9fc</t>
-  </si>
-  <si>
-    <t>99efe2b5-366d-41d5-bd50-cc8c89172454</t>
-  </si>
-  <si>
-    <t>11e24f28-a53e-43a7-93e1-a21aab719045</t>
-  </si>
-  <si>
-    <t>72794a34-2128-4cb8-b9c4-a73c8745d64e</t>
-  </si>
-  <si>
-    <t>2f2096bb-cb30-4429-b00f-82da78ca940d</t>
-  </si>
-  <si>
-    <t>2250b992-9d6a-4c80-8259-50e8485a363d</t>
-  </si>
-  <si>
-    <t>ba377f88-c272-4653-b088-414dfbddaa27</t>
-  </si>
-  <si>
-    <t>16aa934c-6564-4a3e-bf55-477bd1ed3a68</t>
-  </si>
-  <si>
-    <t>36b4d0ab-497c-4f61-9b8f-a068fdde642c</t>
-  </si>
-  <si>
-    <t>47a45f4e-cc69-4781-8efb-f0769e59ac4b</t>
-  </si>
-  <si>
-    <t>7027d585-5012-43e8-ab09-063650ac845d</t>
-  </si>
-  <si>
-    <t>c030328b-64c9-4507-a610-f2691dd79804</t>
-  </si>
-  <si>
-    <t>9b417d1d-07f2-4dfb-ac96-d02c0974f394</t>
-  </si>
-  <si>
-    <t>339f78ae-ab73-43c7-8b29-8314fe185b24</t>
-  </si>
-  <si>
-    <t>8bc6c1f4-0f36-46fe-863e-66c7fcbd96e7</t>
-  </si>
-  <si>
-    <t>246f5066-497a-4418-9aa3-f4188f2c89d9</t>
-  </si>
-  <si>
-    <t>af55b0dd-712f-4e2c-a05f-b3ec606aa811</t>
-  </si>
-  <si>
-    <t>6aad7c3a-c50e-4381-993a-02c7e340bad6</t>
-  </si>
-  <si>
-    <t>0b46e83c-b8b0-49d1-81c4-6e75aafc5c4d</t>
-  </si>
-  <si>
-    <t>7d4e6c95-6817-427a-a34d-70ecc005403c</t>
-  </si>
-  <si>
-    <t>bf3eeb2f-6905-42e2-8a84-8bfdd849c230</t>
-  </si>
-  <si>
-    <t>9e811c4f-16b8-4892-a3b9-329ffa11ad5a</t>
-  </si>
-  <si>
-    <t>e0e7e059-4a63-47b0-b056-628a1d8dff5a</t>
-  </si>
-  <si>
-    <t>3aae4f08-a9b6-45c0-91ed-3d119337cfaa</t>
-  </si>
-  <si>
-    <t>55968f05-af8b-4517-9feb-ed1b89eef2d3</t>
-  </si>
-  <si>
-    <t>6f92a3aa-95a9-4e4b-9fbb-bbe781591b47</t>
-  </si>
-  <si>
-    <t>f689740a-551a-45e7-822f-418eb3da6b00</t>
-  </si>
-  <si>
-    <t>e9800206-8524-4371-8a30-f900919ce25b</t>
-  </si>
-  <si>
-    <t>5f52cbb8-bb8d-46cf-9fa7-719978353711</t>
-  </si>
-  <si>
-    <t>08101094-8561-4275-8ad8-932ec134ac66</t>
-  </si>
-  <si>
-    <t>9bd6dc80-4d02-4758-8b2d-009576906cf3</t>
-  </si>
-  <si>
-    <t>e7567fb1-5401-47d9-8cbd-f371f57ef72a</t>
-  </si>
-  <si>
-    <t>4c86547c-be31-4c09-84b1-4750d0128200</t>
-  </si>
-  <si>
-    <t>7d7be2a6-a8a7-4884-a5e8-1bbe5a1a5783</t>
-  </si>
-  <si>
-    <t>ba39552a-6651-4804-b8ed-b215ccda123e</t>
-  </si>
-  <si>
-    <t>26f629fd-4969-4aa8-9324-ac4a37568160</t>
-  </si>
-  <si>
-    <t>da7b6560-09b0-4e7f-9a15-7e63844a242e</t>
-  </si>
-  <si>
-    <t>97446a2b-266c-4e17-aa5e-234e8e3e252b</t>
-  </si>
-  <si>
-    <t>bf05e09f-0de6-4343-bb82-a25331b06f4f</t>
-  </si>
-  <si>
-    <t>0e00edcf-fe49-489a-8f29-bced7aa6ae09</t>
-  </si>
-  <si>
-    <t>6f2477cc-efe7-4dc2-84db-2deb37cb7da7</t>
-  </si>
-  <si>
-    <t>f7323fa7-e9c3-4a83-89d0-ac9d317b1efb</t>
-  </si>
-  <si>
-    <t>194c40f1-37d8-43f3-8ed7-0113c35ba40d</t>
-  </si>
-  <si>
-    <t>703fbd73-57b2-403c-a8e6-39df9b258dfd</t>
-  </si>
-  <si>
-    <t>15d10fc1-dddd-4c98-b9b6-c9a0f39550e7</t>
-  </si>
-  <si>
-    <t>d482f3bb-9c33-4046-a36b-3c7ee6ef1663</t>
-  </si>
-  <si>
-    <t>62479591-94d2-4ef7-a834-cae87f381383</t>
-  </si>
-  <si>
-    <t>ca86e696-bd55-414c-b38f-fee5e034a3e9</t>
-  </si>
-  <si>
-    <t>e02b1b3c-7247-41a6-9ddb-166952df5d3d</t>
-  </si>
-  <si>
-    <t>b107f0ed-6116-43d7-807c-c7e43065be2f</t>
-  </si>
-  <si>
-    <t>6d568953-050f-4bea-b803-4b786956c5ae</t>
-  </si>
-  <si>
-    <t>dfb92c50-c40a-4168-941b-c87af3270f95</t>
-  </si>
-  <si>
-    <t>741b6837-5d16-4c96-8f17-2ebedbd493c7</t>
-  </si>
-  <si>
-    <t>f4b57015-ecd3-4656-a441-17a064320194</t>
-  </si>
-  <si>
-    <t>3db28621-e212-4bef-a1a6-485f0cd5c6d0</t>
-  </si>
-  <si>
-    <t>ce918d78-4a5b-4e61-9c26-c354b03edd0c</t>
-  </si>
-  <si>
-    <t>02306e58-4dca-4124-8d6d-c25928ec0980</t>
-  </si>
-  <si>
-    <t>f81c05ee-a3fa-4f88-b77f-87f315e6ad67</t>
-  </si>
-  <si>
-    <t>ZX Spectrum/Spectrum+ Service Manual</t>
-  </si>
-  <si>
-    <t>ZX Spectrum/Shared files/Board local files/ZX-Spectrum-Service-Manual.pdf</t>
-  </si>
-  <si>
-    <t>5b1f5209-250a-4414-8434-126bb53e2fb2</t>
+    <t>Generic shared files/Component images/4532.png</t>
+  </si>
+  <si>
+    <t>05fd6847-6b82-4e52-a500-34cf2360375a</t>
+  </si>
+  <si>
+    <t>37b444bb-7c2f-405b-8fe1-4273d3c1260e</t>
+  </si>
+  <si>
+    <t>5e45da1f-f655-44ea-b3cb-df0d3f9d946c</t>
+  </si>
+  <si>
+    <t>b776342a-cc31-4c63-b14a-3af414406ee2</t>
+  </si>
+  <si>
+    <t>f286b702-f7ad-47a6-a1b3-fee0888d16aa</t>
+  </si>
+  <si>
+    <t>8d54b5f4-6e6e-42f0-9309-79467ff214bd</t>
+  </si>
+  <si>
+    <t>b6ae036b-915a-4a61-ab03-a41ddc4e5cce</t>
+  </si>
+  <si>
+    <t>f8161ce7-06c7-4d84-855a-f3e76861e842</t>
   </si>
 </sst>
 </file>
@@ -3273,7 +3300,7 @@
     </row>
     <row r="3" spans="1:9" s="10" customFormat="1" ht="21">
       <c r="A3" s="10" t="s">
-        <v>627</v>
+        <v>859</v>
       </c>
       <c r="I3"/>
     </row>
@@ -9691,7 +9718,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D2A4B1-8E0B-46C6-8B83-02048610537D}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:M317"/>
+  <dimension ref="A1:M325"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
@@ -9825,7 +9852,7 @@
         <v>335</v>
       </c>
       <c r="K9" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="72">
@@ -9844,7 +9871,7 @@
         <v>335</v>
       </c>
       <c r="K10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="72">
@@ -9863,7 +9890,7 @@
         <v>335</v>
       </c>
       <c r="K11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="72">
@@ -9882,7 +9909,7 @@
         <v>335</v>
       </c>
       <c r="K12" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="72">
@@ -9901,7 +9928,7 @@
         <v>335</v>
       </c>
       <c r="K13" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="72">
@@ -9920,7 +9947,7 @@
         <v>335</v>
       </c>
       <c r="K14" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="72">
@@ -9939,7 +9966,7 @@
         <v>335</v>
       </c>
       <c r="K15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="72">
@@ -9958,7 +9985,7 @@
         <v>335</v>
       </c>
       <c r="K16" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="72">
@@ -9977,7 +10004,7 @@
         <v>270</v>
       </c>
       <c r="K17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="72">
@@ -9996,7 +10023,7 @@
         <v>335</v>
       </c>
       <c r="K18" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="72">
@@ -10015,7 +10042,7 @@
         <v>270</v>
       </c>
       <c r="K19" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="72">
@@ -10034,7 +10061,7 @@
         <v>270</v>
       </c>
       <c r="K20" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="72">
@@ -10053,7 +10080,7 @@
         <v>335</v>
       </c>
       <c r="K21" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="72">
@@ -10072,7 +10099,7 @@
         <v>335</v>
       </c>
       <c r="K22" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="72">
@@ -10091,7 +10118,7 @@
         <v>335</v>
       </c>
       <c r="K23" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="72">
@@ -10110,7 +10137,7 @@
         <v>335</v>
       </c>
       <c r="K24" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="72">
@@ -10129,7 +10156,7 @@
         <v>335</v>
       </c>
       <c r="K25" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="72">
@@ -10148,7 +10175,7 @@
         <v>270</v>
       </c>
       <c r="K26" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="72">
@@ -10167,7 +10194,7 @@
         <v>335</v>
       </c>
       <c r="K27" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="72">
@@ -10186,7 +10213,7 @@
         <v>335</v>
       </c>
       <c r="K28" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="72">
@@ -10205,7 +10232,7 @@
         <v>335</v>
       </c>
       <c r="K29" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="72">
@@ -10224,7 +10251,7 @@
         <v>335</v>
       </c>
       <c r="K30" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="72">
@@ -10243,7 +10270,7 @@
         <v>335</v>
       </c>
       <c r="K31" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="72">
@@ -10262,7 +10289,7 @@
         <v>335</v>
       </c>
       <c r="K32" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="72">
@@ -10281,7 +10308,7 @@
         <v>335</v>
       </c>
       <c r="K33" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="72">
@@ -10300,7 +10327,7 @@
         <v>335</v>
       </c>
       <c r="K34" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="72">
@@ -10319,7 +10346,7 @@
         <v>270</v>
       </c>
       <c r="K35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="72">
@@ -10338,7 +10365,7 @@
         <v>270</v>
       </c>
       <c r="K36" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="72">
@@ -10357,7 +10384,7 @@
         <v>270</v>
       </c>
       <c r="K37" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="72">
@@ -10376,7 +10403,7 @@
         <v>335</v>
       </c>
       <c r="K38" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="72">
@@ -10395,7 +10422,7 @@
         <v>335</v>
       </c>
       <c r="K39" s="42" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="72">
@@ -10414,7 +10441,7 @@
         <v>270</v>
       </c>
       <c r="K40" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="72">
@@ -10433,7 +10460,7 @@
         <v>335</v>
       </c>
       <c r="K41" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="72">
@@ -10452,7 +10479,7 @@
         <v>335</v>
       </c>
       <c r="K42" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="72">
@@ -10471,7 +10498,7 @@
         <v>335</v>
       </c>
       <c r="K43" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="72">
@@ -10490,7 +10517,7 @@
         <v>335</v>
       </c>
       <c r="K44" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="72">
@@ -10509,7 +10536,7 @@
         <v>335</v>
       </c>
       <c r="K45" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="72">
@@ -10528,7 +10555,7 @@
         <v>335</v>
       </c>
       <c r="K46" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="72">
@@ -10547,7 +10574,7 @@
         <v>335</v>
       </c>
       <c r="K47" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="72">
@@ -10566,7 +10593,7 @@
         <v>335</v>
       </c>
       <c r="K48" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="72">
@@ -10585,7 +10612,7 @@
         <v>335</v>
       </c>
       <c r="K49" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="72">
@@ -10604,7 +10631,7 @@
         <v>335</v>
       </c>
       <c r="K50" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="72">
@@ -10623,7 +10650,7 @@
         <v>335</v>
       </c>
       <c r="K51" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="72">
@@ -10642,7 +10669,7 @@
         <v>270</v>
       </c>
       <c r="K52" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="72">
@@ -10661,7 +10688,7 @@
         <v>335</v>
       </c>
       <c r="K53" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="72">
@@ -10680,7 +10707,7 @@
         <v>335</v>
       </c>
       <c r="K54" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="72">
@@ -10699,7 +10726,7 @@
         <v>335</v>
       </c>
       <c r="K55" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="72">
@@ -10718,7 +10745,7 @@
         <v>335</v>
       </c>
       <c r="K56" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="72">
@@ -10737,7 +10764,7 @@
         <v>335</v>
       </c>
       <c r="K57" s="42" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="72">
@@ -10756,7 +10783,7 @@
         <v>335</v>
       </c>
       <c r="K58" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="72">
@@ -10775,7 +10802,7 @@
         <v>335</v>
       </c>
       <c r="K59" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="72">
@@ -10794,7 +10821,7 @@
         <v>335</v>
       </c>
       <c r="K60" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="72">
@@ -10813,7 +10840,7 @@
         <v>270</v>
       </c>
       <c r="K61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="72">
@@ -10832,7 +10859,7 @@
         <v>335</v>
       </c>
       <c r="K62" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="72">
@@ -10851,7 +10878,7 @@
         <v>335</v>
       </c>
       <c r="K63" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="72">
@@ -10870,7 +10897,7 @@
         <v>270</v>
       </c>
       <c r="K64" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="72">
@@ -10889,7 +10916,7 @@
         <v>270</v>
       </c>
       <c r="K65" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -10908,7 +10935,7 @@
         <v>575</v>
       </c>
       <c r="K66" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -10927,7 +10954,7 @@
         <v>575</v>
       </c>
       <c r="K67" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -10946,7 +10973,7 @@
         <v>575</v>
       </c>
       <c r="K68" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -10965,7 +10992,7 @@
         <v>575</v>
       </c>
       <c r="K69" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -10984,7 +11011,7 @@
         <v>575</v>
       </c>
       <c r="K70" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -11003,7 +11030,7 @@
         <v>575</v>
       </c>
       <c r="K71" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -11022,7 +11049,7 @@
         <v>575</v>
       </c>
       <c r="K72" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -11041,7 +11068,7 @@
         <v>575</v>
       </c>
       <c r="K73" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -11060,7 +11087,7 @@
         <v>575</v>
       </c>
       <c r="K74" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -11079,7 +11106,7 @@
         <v>575</v>
       </c>
       <c r="K75" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -11098,7 +11125,7 @@
         <v>575</v>
       </c>
       <c r="K76" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -11117,7 +11144,7 @@
         <v>575</v>
       </c>
       <c r="K77" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -11136,7 +11163,7 @@
         <v>575</v>
       </c>
       <c r="K78" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -11155,7 +11182,7 @@
         <v>575</v>
       </c>
       <c r="K79" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -11169,7 +11196,7 @@
         <v>584</v>
       </c>
       <c r="K80" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -11188,7 +11215,7 @@
         <v>583</v>
       </c>
       <c r="K81" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -11207,7 +11234,7 @@
         <v>583</v>
       </c>
       <c r="K82" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -11226,7 +11253,7 @@
         <v>583</v>
       </c>
       <c r="K83" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -11245,7 +11272,7 @@
         <v>583</v>
       </c>
       <c r="K84" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -11264,7 +11291,7 @@
         <v>583</v>
       </c>
       <c r="K85" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -11283,7 +11310,7 @@
         <v>583</v>
       </c>
       <c r="K86" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -11302,7 +11329,7 @@
         <v>583</v>
       </c>
       <c r="K87" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -11321,12 +11348,12 @@
         <v>583</v>
       </c>
       <c r="K88" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B89" s="13"/>
       <c r="C89" s="29"/>
@@ -11334,33 +11361,33 @@
         <v>267</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>585</v>
+        <v>860</v>
       </c>
       <c r="J89" s="32"/>
       <c r="K89" t="s">
-        <v>708</v>
+        <v>861</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B90" s="13"/>
       <c r="C90" s="29"/>
       <c r="D90" s="11" t="s">
-        <v>375</v>
+        <v>267</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>586</v>
+        <v>860</v>
       </c>
       <c r="J90" s="32"/>
       <c r="K90" t="s">
-        <v>709</v>
+        <v>862</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B91" s="13"/>
       <c r="C91" s="29"/>
@@ -11368,33 +11395,33 @@
         <v>267</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>587</v>
+        <v>860</v>
       </c>
       <c r="J91" s="32"/>
       <c r="K91" t="s">
-        <v>710</v>
+        <v>863</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B92" s="13"/>
       <c r="C92" s="29"/>
       <c r="D92" s="11" t="s">
-        <v>375</v>
+        <v>267</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>588</v>
+        <v>860</v>
       </c>
       <c r="J92" s="32"/>
       <c r="K92" t="s">
-        <v>711</v>
+        <v>864</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B93" s="13"/>
       <c r="C93" s="29"/>
@@ -11402,164 +11429,152 @@
         <v>267</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>591</v>
+        <v>860</v>
       </c>
       <c r="J93" s="32"/>
       <c r="K93" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="28.8">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="B94" s="13"/>
+      <c r="C94" s="29"/>
       <c r="D94" s="11" t="s">
         <v>267</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="J94" s="32" t="s">
-        <v>360</v>
-      </c>
+        <v>860</v>
+      </c>
+      <c r="J94" s="32"/>
       <c r="K94" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="28.8">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>169</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="B95" s="13"/>
+      <c r="C95" s="29"/>
       <c r="D95" s="11" t="s">
-        <v>375</v>
+        <v>267</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="J95" s="32" t="s">
-        <v>360</v>
-      </c>
+        <v>860</v>
+      </c>
+      <c r="J95" s="32"/>
       <c r="K95" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="28.8">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="B96" s="13"/>
+      <c r="C96" s="29"/>
       <c r="D96" s="11" t="s">
         <v>267</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="J96" s="32" t="s">
-        <v>360</v>
-      </c>
+        <v>860</v>
+      </c>
+      <c r="J96" s="32"/>
       <c r="K96" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="28.8">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>171</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="B97" s="13"/>
+      <c r="C97" s="29"/>
       <c r="D97" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="I97" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="J97" s="32"/>
+      <c r="K97" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B98" s="13"/>
+      <c r="C98" s="29"/>
+      <c r="D98" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="I97" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="J97" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="K97" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="28.8">
-      <c r="A98" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D98" s="11" t="s">
+      <c r="I98" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="J98" s="32"/>
+      <c r="K98" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B99" s="13"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="I98" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="J98" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="K98" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="28.8">
-      <c r="A99" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D99" s="11" t="s">
+      <c r="I99" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="J99" s="32"/>
+      <c r="K99" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B100" s="13"/>
+      <c r="C100" s="29"/>
+      <c r="D100" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="I99" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="J99" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="K99" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="28.8">
-      <c r="A100" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D100" s="11" t="s">
+      <c r="I100" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="J100" s="32"/>
+      <c r="K100" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B101" s="13"/>
+      <c r="C101" s="29"/>
+      <c r="D101" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="I100" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="J100" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="K100" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" ht="28.8">
-      <c r="A101" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D101" s="11" t="s">
-        <v>375</v>
-      </c>
       <c r="I101" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="J101" s="32" t="s">
-        <v>360</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="J101" s="32"/>
       <c r="K101" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="28.8">
       <c r="A102" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>37</v>
@@ -11574,12 +11589,12 @@
         <v>360</v>
       </c>
       <c r="K102" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="28.8">
       <c r="A103" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>375</v>
@@ -11591,12 +11606,12 @@
         <v>360</v>
       </c>
       <c r="K103" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="28.8">
       <c r="A104" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>37</v>
@@ -11611,12 +11626,12 @@
         <v>360</v>
       </c>
       <c r="K104" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="28.8">
       <c r="A105" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>375</v>
@@ -11628,12 +11643,12 @@
         <v>360</v>
       </c>
       <c r="K105" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="28.8">
       <c r="A106" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>37</v>
@@ -11648,12 +11663,12 @@
         <v>360</v>
       </c>
       <c r="K106" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="28.8">
       <c r="A107" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D107" s="11" t="s">
         <v>375</v>
@@ -11665,12 +11680,12 @@
         <v>360</v>
       </c>
       <c r="K107" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="28.8">
       <c r="A108" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>37</v>
@@ -11685,12 +11700,12 @@
         <v>360</v>
       </c>
       <c r="K108" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="28.8">
       <c r="A109" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D109" s="11" t="s">
         <v>375</v>
@@ -11702,12 +11717,12 @@
         <v>360</v>
       </c>
       <c r="K109" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="28.8">
       <c r="A110" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>37</v>
@@ -11716,18 +11731,18 @@
         <v>267</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J110" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K110" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="28.8">
       <c r="A111" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D111" s="11" t="s">
         <v>375</v>
@@ -11739,12 +11754,12 @@
         <v>360</v>
       </c>
       <c r="K111" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="28.8">
       <c r="A112" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>37</v>
@@ -11753,18 +11768,18 @@
         <v>267</v>
       </c>
       <c r="I112" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J112" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K112" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="28.8">
       <c r="A113" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>375</v>
@@ -11776,12 +11791,12 @@
         <v>360</v>
       </c>
       <c r="K113" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="28.8">
       <c r="A114" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>37</v>
@@ -11790,18 +11805,18 @@
         <v>267</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J114" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K114" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="28.8">
       <c r="A115" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D115" s="11" t="s">
         <v>375</v>
@@ -11813,12 +11828,12 @@
         <v>360</v>
       </c>
       <c r="K115" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="28.8">
       <c r="A116" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>37</v>
@@ -11827,18 +11842,18 @@
         <v>267</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J116" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K116" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="28.8">
       <c r="A117" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D117" s="11" t="s">
         <v>375</v>
@@ -11850,12 +11865,12 @@
         <v>360</v>
       </c>
       <c r="K117" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="28.8">
       <c r="A118" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>37</v>
@@ -11870,12 +11885,12 @@
         <v>360</v>
       </c>
       <c r="K118" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="28.8">
       <c r="A119" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D119" s="11" t="s">
         <v>375</v>
@@ -11887,12 +11902,12 @@
         <v>360</v>
       </c>
       <c r="K119" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="28.8">
       <c r="A120" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>37</v>
@@ -11907,12 +11922,12 @@
         <v>360</v>
       </c>
       <c r="K120" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="28.8">
       <c r="A121" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D121" s="11" t="s">
         <v>375</v>
@@ -11924,12 +11939,12 @@
         <v>360</v>
       </c>
       <c r="K121" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="28.8">
       <c r="A122" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>37</v>
@@ -11944,12 +11959,12 @@
         <v>360</v>
       </c>
       <c r="K122" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="28.8">
       <c r="A123" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D123" s="11" t="s">
         <v>375</v>
@@ -11961,12 +11976,12 @@
         <v>360</v>
       </c>
       <c r="K123" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="28.8">
       <c r="A124" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>37</v>
@@ -11981,12 +11996,12 @@
         <v>360</v>
       </c>
       <c r="K124" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="28.8">
       <c r="A125" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D125" s="11" t="s">
         <v>375</v>
@@ -11998,12 +12013,12 @@
         <v>360</v>
       </c>
       <c r="K125" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="28.8">
       <c r="A126" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>37</v>
@@ -12012,18 +12027,18 @@
         <v>267</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J126" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K126" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="28.8">
       <c r="A127" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D127" s="11" t="s">
         <v>375</v>
@@ -12035,12 +12050,12 @@
         <v>360</v>
       </c>
       <c r="K127" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="28.8">
       <c r="A128" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>37</v>
@@ -12049,18 +12064,18 @@
         <v>267</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J128" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K128" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="28.8">
       <c r="A129" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D129" s="11" t="s">
         <v>375</v>
@@ -12072,12 +12087,12 @@
         <v>360</v>
       </c>
       <c r="K129" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="28.8">
       <c r="A130" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>37</v>
@@ -12086,18 +12101,18 @@
         <v>267</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J130" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K130" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="28.8">
       <c r="A131" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D131" s="11" t="s">
         <v>375</v>
@@ -12109,44 +12124,36 @@
         <v>360</v>
       </c>
       <c r="K131" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="28.8">
       <c r="A132" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="E132" s="32"/>
-      <c r="F132" s="32"/>
-      <c r="G132" s="32"/>
-      <c r="H132" s="32"/>
       <c r="I132" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J132" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K132" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="28.8">
       <c r="A133" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D133" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D133" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="E133" s="32"/>
-      <c r="F133" s="32"/>
-      <c r="G133" s="32"/>
-      <c r="H133" s="32"/>
       <c r="I133" s="11" t="s">
         <v>359</v>
       </c>
@@ -12154,17 +12161,17 @@
         <v>360</v>
       </c>
       <c r="K133" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="28.8">
       <c r="A134" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" s="11" t="s">
         <v>267</v>
       </c>
       <c r="I134" s="11" t="s">
@@ -12174,14 +12181,14 @@
         <v>360</v>
       </c>
       <c r="K134" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="28.8">
       <c r="A135" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D135" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D135" s="11" t="s">
         <v>375</v>
       </c>
       <c r="I135" s="11" t="s">
@@ -12191,17 +12198,17 @@
         <v>360</v>
       </c>
       <c r="K135" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="28.8">
       <c r="A136" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="11" t="s">
         <v>267</v>
       </c>
       <c r="I136" s="11" t="s">
@@ -12211,14 +12218,14 @@
         <v>360</v>
       </c>
       <c r="K136" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="28.8">
       <c r="A137" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D137" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D137" s="11" t="s">
         <v>375</v>
       </c>
       <c r="I137" s="11" t="s">
@@ -12228,17 +12235,17 @@
         <v>360</v>
       </c>
       <c r="K137" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="28.8">
       <c r="A138" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" s="11" t="s">
         <v>267</v>
       </c>
       <c r="I138" s="11" t="s">
@@ -12248,14 +12255,14 @@
         <v>360</v>
       </c>
       <c r="K138" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="28.8">
       <c r="A139" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D139" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D139" s="11" t="s">
         <v>375</v>
       </c>
       <c r="I139" s="11" t="s">
@@ -12265,12 +12272,12 @@
         <v>360</v>
       </c>
       <c r="K139" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="28.8">
       <c r="A140" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>37</v>
@@ -12278,36 +12285,44 @@
       <c r="D140" s="1" t="s">
         <v>267</v>
       </c>
+      <c r="E140" s="32"/>
+      <c r="F140" s="32"/>
+      <c r="G140" s="32"/>
+      <c r="H140" s="32"/>
       <c r="I140" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J140" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K140" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="28.8">
       <c r="A141" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>375</v>
       </c>
+      <c r="E141" s="32"/>
+      <c r="F141" s="32"/>
+      <c r="G141" s="32"/>
+      <c r="H141" s="32"/>
       <c r="I141" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J141" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="K141" s="42" t="s">
-        <v>760</v>
+      <c r="K141" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="28.8">
       <c r="A142" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>37</v>
@@ -12316,18 +12331,18 @@
         <v>267</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J142" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K142" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="28.8">
       <c r="A143" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>375</v>
@@ -12339,33 +12354,34 @@
         <v>360</v>
       </c>
       <c r="K143" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="28.8">
-      <c r="A144" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="B144" s="34"/>
-      <c r="D144" s="33" t="s">
+      <c r="A144" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>267</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J144" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K144" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="28.8">
-      <c r="A145" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="B145" s="34"/>
-      <c r="D145" s="33" t="s">
+      <c r="A145" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>375</v>
       </c>
       <c r="I145" s="11" t="s">
@@ -12375,33 +12391,34 @@
         <v>360</v>
       </c>
       <c r="K145" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="28.8">
-      <c r="A146" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="B146" s="34"/>
-      <c r="D146" s="33" t="s">
+      <c r="A146" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>267</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J146" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K146" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="28.8">
-      <c r="A147" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="B147" s="34"/>
-      <c r="D147" s="33" t="s">
+      <c r="A147" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>375</v>
       </c>
       <c r="I147" s="11" t="s">
@@ -12411,34 +12428,34 @@
         <v>360</v>
       </c>
       <c r="K147" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="28.8">
       <c r="A148" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D148" s="33" t="s">
+      <c r="D148" s="1" t="s">
         <v>267</v>
       </c>
       <c r="I148" s="11" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J148" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K148" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="28.8">
       <c r="A149" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D149" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>375</v>
       </c>
       <c r="I149" s="11" t="s">
@@ -12447,35 +12464,35 @@
       <c r="J149" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="K149" t="s">
-        <v>768</v>
+      <c r="K149" s="42" t="s">
+        <v>759</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="28.8">
       <c r="A150" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D150" s="33" t="s">
+      <c r="D150" s="1" t="s">
         <v>267</v>
       </c>
       <c r="I150" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J150" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K150" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="28.8">
       <c r="A151" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D151" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>375</v>
       </c>
       <c r="I151" s="11" t="s">
@@ -12485,33 +12502,32 @@
         <v>360</v>
       </c>
       <c r="K151" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="28.8">
-      <c r="A152" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A152" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B152" s="34"/>
       <c r="D152" s="33" t="s">
         <v>267</v>
       </c>
       <c r="I152" s="11" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="J152" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K152" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="28.8">
-      <c r="A153" s="1" t="s">
-        <v>199</v>
-      </c>
+      <c r="A153" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B153" s="34"/>
       <c r="D153" s="33" t="s">
         <v>375</v>
       </c>
@@ -12522,33 +12538,32 @@
         <v>360</v>
       </c>
       <c r="K153" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="28.8">
-      <c r="A154" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A154" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B154" s="34"/>
       <c r="D154" s="33" t="s">
         <v>267</v>
       </c>
       <c r="I154" s="11" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="J154" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K154" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="28.8">
-      <c r="A155" s="1" t="s">
-        <v>200</v>
-      </c>
+      <c r="A155" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B155" s="34"/>
       <c r="D155" s="33" t="s">
         <v>375</v>
       </c>
@@ -12559,12 +12574,12 @@
         <v>360</v>
       </c>
       <c r="K155" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="28.8">
       <c r="A156" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>37</v>
@@ -12573,18 +12588,18 @@
         <v>267</v>
       </c>
       <c r="I156" s="11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="J156" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K156" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="28.8">
       <c r="A157" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D157" s="33" t="s">
         <v>375</v>
@@ -12596,12 +12611,12 @@
         <v>360</v>
       </c>
       <c r="K157" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="28.8">
       <c r="A158" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>37</v>
@@ -12610,18 +12625,18 @@
         <v>267</v>
       </c>
       <c r="I158" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J158" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K158" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="28.8">
       <c r="A159" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D159" s="33" t="s">
         <v>375</v>
@@ -12633,34 +12648,34 @@
         <v>360</v>
       </c>
       <c r="K159" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="28.8">
       <c r="A160" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="D160" s="33" t="s">
         <v>267</v>
       </c>
       <c r="I160" s="11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J160" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K160" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="28.8">
       <c r="A161" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D161" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D161" s="33" t="s">
         <v>375</v>
       </c>
       <c r="I161" s="11" t="s">
@@ -12670,17 +12685,17 @@
         <v>360</v>
       </c>
       <c r="K161" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
     </row>
     <row r="162" spans="1:11" ht="28.8">
       <c r="A162" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="D162" s="33" t="s">
         <v>267</v>
       </c>
       <c r="I162" s="11" t="s">
@@ -12690,14 +12705,14 @@
         <v>360</v>
       </c>
       <c r="K162" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="28.8">
       <c r="A163" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D163" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D163" s="33" t="s">
         <v>375</v>
       </c>
       <c r="I163" s="11" t="s">
@@ -12707,34 +12722,34 @@
         <v>360</v>
       </c>
       <c r="K163" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="28.8">
       <c r="A164" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="D164" s="33" t="s">
         <v>267</v>
       </c>
       <c r="I164" s="11" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J164" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K164" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="28.8">
       <c r="A165" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D165" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D165" s="33" t="s">
         <v>375</v>
       </c>
       <c r="I165" s="11" t="s">
@@ -12744,34 +12759,34 @@
         <v>360</v>
       </c>
       <c r="K165" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="28.8">
       <c r="A166" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="D166" s="33" t="s">
         <v>267</v>
       </c>
       <c r="I166" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J166" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K166" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="28.8">
       <c r="A167" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D167" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D167" s="33" t="s">
         <v>375</v>
       </c>
       <c r="I167" s="11" t="s">
@@ -12781,12 +12796,12 @@
         <v>360</v>
       </c>
       <c r="K167" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="28.8">
       <c r="A168" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>37</v>
@@ -12794,36 +12809,36 @@
       <c r="D168" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I168" s="1" t="s">
-        <v>364</v>
+      <c r="I168" s="11" t="s">
+        <v>368</v>
       </c>
       <c r="J168" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="K168" s="42" t="s">
-        <v>787</v>
+      <c r="K168" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="28.8">
       <c r="A169" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I169" s="1" t="s">
+      <c r="I169" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J169" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K169" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="28.8">
       <c r="A170" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>37</v>
@@ -12831,36 +12846,36 @@
       <c r="D170" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I170" s="1" t="s">
-        <v>369</v>
+      <c r="I170" s="11" t="s">
+        <v>366</v>
       </c>
       <c r="J170" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K170" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
     </row>
     <row r="171" spans="1:11" ht="28.8">
       <c r="A171" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I171" s="1" t="s">
+      <c r="I171" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J171" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K171" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
     </row>
     <row r="172" spans="1:11" ht="28.8">
       <c r="A172" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>37</v>
@@ -12868,36 +12883,36 @@
       <c r="D172" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I172" s="1" t="s">
-        <v>370</v>
+      <c r="I172" s="11" t="s">
+        <v>367</v>
       </c>
       <c r="J172" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K172" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
     </row>
     <row r="173" spans="1:11" ht="28.8">
       <c r="A173" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I173" s="1" t="s">
+      <c r="I173" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J173" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K173" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
     </row>
     <row r="174" spans="1:11" ht="28.8">
       <c r="A174" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>37</v>
@@ -12905,44 +12920,36 @@
       <c r="D174" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E174" s="32"/>
-      <c r="F174" s="32"/>
-      <c r="G174" s="32"/>
-      <c r="H174" s="32"/>
-      <c r="I174" s="1" t="s">
+      <c r="I174" s="11" t="s">
         <v>364</v>
       </c>
       <c r="J174" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K174" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
     </row>
     <row r="175" spans="1:11" ht="28.8">
       <c r="A175" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="E175" s="32"/>
-      <c r="F175" s="32"/>
-      <c r="G175" s="32"/>
-      <c r="H175" s="32"/>
-      <c r="I175" s="1" t="s">
+      <c r="I175" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J175" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K175" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
     </row>
     <row r="176" spans="1:11" ht="28.8">
       <c r="A176" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>37</v>
@@ -12956,13 +12963,13 @@
       <c r="J176" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="K176" t="s">
-        <v>795</v>
+      <c r="K176" s="42" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="177" spans="1:11" ht="28.8">
       <c r="A177" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>375</v>
@@ -12974,12 +12981,12 @@
         <v>360</v>
       </c>
       <c r="K177" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
     </row>
     <row r="178" spans="1:11" ht="28.8">
       <c r="A178" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>37</v>
@@ -12988,18 +12995,18 @@
         <v>267</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="J178" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K178" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
     </row>
     <row r="179" spans="1:11" ht="28.8">
       <c r="A179" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>375</v>
@@ -13011,12 +13018,12 @@
         <v>360</v>
       </c>
       <c r="K179" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
     </row>
     <row r="180" spans="1:11" ht="28.8">
       <c r="A180" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>37</v>
@@ -13025,18 +13032,18 @@
         <v>267</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="J180" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K180" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
     </row>
     <row r="181" spans="1:11" ht="28.8">
       <c r="A181" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>375</v>
@@ -13048,12 +13055,12 @@
         <v>360</v>
       </c>
       <c r="K181" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
     </row>
     <row r="182" spans="1:11" ht="28.8">
       <c r="A182" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>37</v>
@@ -13061,23 +13068,31 @@
       <c r="D182" s="1" t="s">
         <v>267</v>
       </c>
+      <c r="E182" s="32"/>
+      <c r="F182" s="32"/>
+      <c r="G182" s="32"/>
+      <c r="H182" s="32"/>
       <c r="I182" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J182" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K182" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
     </row>
     <row r="183" spans="1:11" ht="28.8">
       <c r="A183" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>375</v>
       </c>
+      <c r="E183" s="32"/>
+      <c r="F183" s="32"/>
+      <c r="G183" s="32"/>
+      <c r="H183" s="32"/>
       <c r="I183" s="1" t="s">
         <v>359</v>
       </c>
@@ -13085,12 +13100,12 @@
         <v>360</v>
       </c>
       <c r="K183" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
     </row>
     <row r="184" spans="1:11" ht="28.8">
       <c r="A184" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>37</v>
@@ -13099,18 +13114,18 @@
         <v>267</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J184" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K184" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
     </row>
     <row r="185" spans="1:11" ht="28.8">
       <c r="A185" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>375</v>
@@ -13122,12 +13137,12 @@
         <v>360</v>
       </c>
       <c r="K185" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
     </row>
     <row r="186" spans="1:11" ht="28.8">
       <c r="A186" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>37</v>
@@ -13136,18 +13151,18 @@
         <v>267</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="J186" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K186" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
     </row>
     <row r="187" spans="1:11" ht="28.8">
       <c r="A187" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>375</v>
@@ -13159,12 +13174,12 @@
         <v>360</v>
       </c>
       <c r="K187" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
     </row>
     <row r="188" spans="1:11" ht="28.8">
       <c r="A188" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>37</v>
@@ -13173,18 +13188,18 @@
         <v>267</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="J188" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K188" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
     </row>
     <row r="189" spans="1:11" ht="28.8">
       <c r="A189" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>375</v>
@@ -13196,12 +13211,12 @@
         <v>360</v>
       </c>
       <c r="K189" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
     </row>
     <row r="190" spans="1:11" ht="28.8">
       <c r="A190" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>37</v>
@@ -13210,18 +13225,18 @@
         <v>267</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="J190" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K190" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
     </row>
     <row r="191" spans="1:11" ht="28.8">
       <c r="A191" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>375</v>
@@ -13233,12 +13248,12 @@
         <v>360</v>
       </c>
       <c r="K191" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
     </row>
     <row r="192" spans="1:11" ht="28.8">
       <c r="A192" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>37</v>
@@ -13247,18 +13262,18 @@
         <v>267</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J192" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K192" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
     </row>
     <row r="193" spans="1:11" ht="28.8">
       <c r="A193" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>375</v>
@@ -13270,12 +13285,12 @@
         <v>360</v>
       </c>
       <c r="K193" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
     </row>
     <row r="194" spans="1:11" ht="28.8">
       <c r="A194" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>37</v>
@@ -13284,18 +13299,18 @@
         <v>267</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="J194" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K194" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
     </row>
     <row r="195" spans="1:11" ht="28.8">
       <c r="A195" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>375</v>
@@ -13307,12 +13322,12 @@
         <v>360</v>
       </c>
       <c r="K195" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
     </row>
     <row r="196" spans="1:11" ht="28.8">
       <c r="A196" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>37</v>
@@ -13321,18 +13336,18 @@
         <v>267</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="J196" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K196" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
     </row>
     <row r="197" spans="1:11" ht="28.8">
       <c r="A197" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>375</v>
@@ -13344,12 +13359,12 @@
         <v>360</v>
       </c>
       <c r="K197" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
     </row>
     <row r="198" spans="1:11" ht="28.8">
       <c r="A198" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>37</v>
@@ -13358,18 +13373,18 @@
         <v>267</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J198" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K198" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
     </row>
     <row r="199" spans="1:11" ht="28.8">
       <c r="A199" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>375</v>
@@ -13381,12 +13396,12 @@
         <v>360</v>
       </c>
       <c r="K199" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
     </row>
     <row r="200" spans="1:11" ht="28.8">
       <c r="A200" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>37</v>
@@ -13394,36 +13409,36 @@
       <c r="D200" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I200" s="11" t="s">
-        <v>368</v>
+      <c r="I200" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="J200" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K200" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
     </row>
     <row r="201" spans="1:11" ht="28.8">
       <c r="A201" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I201" s="11" t="s">
+      <c r="I201" s="1" t="s">
         <v>359</v>
       </c>
       <c r="J201" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="K201" s="42" t="s">
-        <v>820</v>
+      <c r="K201" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="202" spans="1:11" ht="28.8">
       <c r="A202" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>37</v>
@@ -13431,36 +13446,36 @@
       <c r="D202" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I202" s="11" t="s">
-        <v>368</v>
+      <c r="I202" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="J202" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="K202" s="42" t="s">
-        <v>821</v>
+      <c r="K202" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="203" spans="1:11" ht="28.8">
       <c r="A203" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I203" s="11" t="s">
+      <c r="I203" s="1" t="s">
         <v>359</v>
       </c>
       <c r="J203" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K203" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
     </row>
     <row r="204" spans="1:11" ht="28.8">
       <c r="A204" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>37</v>
@@ -13468,10 +13483,6 @@
       <c r="D204" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E204" s="32"/>
-      <c r="F204" s="32"/>
-      <c r="G204" s="32"/>
-      <c r="H204" s="32"/>
       <c r="I204" s="1" t="s">
         <v>364</v>
       </c>
@@ -13479,20 +13490,16 @@
         <v>360</v>
       </c>
       <c r="K204" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
     </row>
     <row r="205" spans="1:11" ht="28.8">
       <c r="A205" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="E205" s="32"/>
-      <c r="F205" s="32"/>
-      <c r="G205" s="32"/>
-      <c r="H205" s="32"/>
       <c r="I205" s="1" t="s">
         <v>359</v>
       </c>
@@ -13500,12 +13507,12 @@
         <v>360</v>
       </c>
       <c r="K205" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
     </row>
     <row r="206" spans="1:11" ht="28.8">
       <c r="A206" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>37</v>
@@ -13514,18 +13521,18 @@
         <v>267</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="J206" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K206" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
     </row>
     <row r="207" spans="1:11" ht="28.8">
       <c r="A207" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>375</v>
@@ -13537,12 +13544,12 @@
         <v>360</v>
       </c>
       <c r="K207" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
     </row>
     <row r="208" spans="1:11" ht="28.8">
       <c r="A208" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>37</v>
@@ -13551,18 +13558,18 @@
         <v>267</v>
       </c>
       <c r="I208" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J208" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K208" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
     </row>
     <row r="209" spans="1:11" ht="28.8">
       <c r="A209" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>375</v>
@@ -13573,13 +13580,13 @@
       <c r="J209" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="K209" t="s">
-        <v>828</v>
+      <c r="K209" s="42" t="s">
+        <v>819</v>
       </c>
     </row>
     <row r="210" spans="1:11" ht="28.8">
       <c r="A210" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>37</v>
@@ -13588,18 +13595,18 @@
         <v>267</v>
       </c>
       <c r="I210" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J210" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="K210" t="s">
-        <v>829</v>
+      <c r="K210" s="42" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="211" spans="1:11" ht="28.8">
       <c r="A211" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>375</v>
@@ -13611,12 +13618,12 @@
         <v>360</v>
       </c>
       <c r="K211" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
     </row>
     <row r="212" spans="1:11" ht="28.8">
       <c r="A212" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>37</v>
@@ -13624,36 +13631,44 @@
       <c r="D212" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I212" s="11" t="s">
-        <v>366</v>
+      <c r="E212" s="32"/>
+      <c r="F212" s="32"/>
+      <c r="G212" s="32"/>
+      <c r="H212" s="32"/>
+      <c r="I212" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="J212" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K212" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
     </row>
     <row r="213" spans="1:11" ht="28.8">
       <c r="A213" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I213" s="11" t="s">
+      <c r="E213" s="32"/>
+      <c r="F213" s="32"/>
+      <c r="G213" s="32"/>
+      <c r="H213" s="32"/>
+      <c r="I213" s="1" t="s">
         <v>359</v>
       </c>
       <c r="J213" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K213" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
     </row>
     <row r="214" spans="1:11" ht="28.8">
       <c r="A214" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>37</v>
@@ -13661,36 +13676,36 @@
       <c r="D214" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I214" s="11" t="s">
-        <v>366</v>
+      <c r="I214" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="J214" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K214" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
     </row>
     <row r="215" spans="1:11" ht="28.8">
       <c r="A215" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I215" s="11" t="s">
+      <c r="I215" s="1" t="s">
         <v>359</v>
       </c>
       <c r="J215" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K215" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
     </row>
     <row r="216" spans="1:11" ht="28.8">
       <c r="A216" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>37</v>
@@ -13705,12 +13720,12 @@
         <v>360</v>
       </c>
       <c r="K216" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
     </row>
     <row r="217" spans="1:11" ht="28.8">
       <c r="A217" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>375</v>
@@ -13722,12 +13737,12 @@
         <v>360</v>
       </c>
       <c r="K217" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
     </row>
     <row r="218" spans="1:11" ht="28.8">
       <c r="A218" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>37</v>
@@ -13735,36 +13750,36 @@
       <c r="D218" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I218" s="1" t="s">
-        <v>374</v>
+      <c r="I218" s="11" t="s">
+        <v>366</v>
       </c>
       <c r="J218" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K218" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
     </row>
     <row r="219" spans="1:11" ht="28.8">
       <c r="A219" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I219" s="1" t="s">
+      <c r="I219" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J219" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K219" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
     </row>
     <row r="220" spans="1:11" ht="28.8">
       <c r="A220" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>37</v>
@@ -13772,36 +13787,36 @@
       <c r="D220" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I220" s="1" t="s">
-        <v>374</v>
+      <c r="I220" s="11" t="s">
+        <v>366</v>
       </c>
       <c r="J220" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K220" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
     </row>
     <row r="221" spans="1:11" ht="28.8">
       <c r="A221" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I221" s="1" t="s">
+      <c r="I221" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J221" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K221" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
     </row>
     <row r="222" spans="1:11" ht="28.8">
       <c r="A222" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>37</v>
@@ -13809,36 +13824,36 @@
       <c r="D222" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I222" s="1" t="s">
-        <v>358</v>
+      <c r="I222" s="11" t="s">
+        <v>366</v>
       </c>
       <c r="J222" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K222" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
     </row>
     <row r="223" spans="1:11" ht="28.8">
       <c r="A223" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I223" s="1" t="s">
+      <c r="I223" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J223" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K223" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
     </row>
     <row r="224" spans="1:11" ht="28.8">
       <c r="A224" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>37</v>
@@ -13846,36 +13861,36 @@
       <c r="D224" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I224" s="1" t="s">
-        <v>364</v>
+      <c r="I224" s="11" t="s">
+        <v>366</v>
       </c>
       <c r="J224" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K224" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
     </row>
     <row r="225" spans="1:11" ht="28.8">
       <c r="A225" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I225" s="1" t="s">
+      <c r="I225" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J225" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K225" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
     </row>
     <row r="226" spans="1:11" ht="28.8">
       <c r="A226" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>37</v>
@@ -13883,36 +13898,36 @@
       <c r="D226" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I226" s="11" t="s">
-        <v>366</v>
+      <c r="I226" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="J226" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K226" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
     </row>
     <row r="227" spans="1:11" ht="28.8">
       <c r="A227" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I227" s="11" t="s">
+      <c r="I227" s="1" t="s">
         <v>359</v>
       </c>
       <c r="J227" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K227" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
     </row>
     <row r="228" spans="1:11" ht="28.8">
       <c r="A228" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>37</v>
@@ -13920,36 +13935,36 @@
       <c r="D228" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I228" s="11" t="s">
-        <v>366</v>
+      <c r="I228" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="J228" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K228" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
     </row>
     <row r="229" spans="1:11" ht="28.8">
       <c r="A229" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I229" s="11" t="s">
+      <c r="I229" s="1" t="s">
         <v>359</v>
       </c>
       <c r="J229" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K229" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
     </row>
     <row r="230" spans="1:11" ht="28.8">
       <c r="A230" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>37</v>
@@ -13958,18 +13973,18 @@
         <v>267</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="J230" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K230" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
     </row>
     <row r="231" spans="1:11" ht="28.8">
       <c r="A231" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>375</v>
@@ -13981,12 +13996,12 @@
         <v>360</v>
       </c>
       <c r="K231" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
     </row>
     <row r="232" spans="1:11" ht="28.8">
       <c r="A232" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>37</v>
@@ -14001,12 +14016,12 @@
         <v>360</v>
       </c>
       <c r="K232" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
     </row>
     <row r="233" spans="1:11" ht="28.8">
       <c r="A233" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>375</v>
@@ -14018,12 +14033,12 @@
         <v>360</v>
       </c>
       <c r="K233" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
     </row>
     <row r="234" spans="1:11" ht="28.8">
       <c r="A234" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>37</v>
@@ -14031,44 +14046,36 @@
       <c r="D234" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E234" s="32"/>
-      <c r="F234" s="32"/>
-      <c r="G234" s="32"/>
-      <c r="H234" s="32"/>
-      <c r="I234" s="1" t="s">
-        <v>361</v>
+      <c r="I234" s="11" t="s">
+        <v>366</v>
       </c>
       <c r="J234" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K234" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
     </row>
     <row r="235" spans="1:11" ht="28.8">
       <c r="A235" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="E235" s="32"/>
-      <c r="F235" s="32"/>
-      <c r="G235" s="32"/>
-      <c r="H235" s="32"/>
-      <c r="I235" s="1" t="s">
+      <c r="I235" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J235" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K235" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
     </row>
     <row r="236" spans="1:11" ht="28.8">
       <c r="A236" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>37</v>
@@ -14076,126 +14083,282 @@
       <c r="D236" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I236" s="1" t="s">
-        <v>371</v>
+      <c r="I236" s="11" t="s">
+        <v>366</v>
       </c>
       <c r="J236" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K236" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
     </row>
     <row r="237" spans="1:11" ht="28.8">
       <c r="A237" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I237" s="1" t="s">
+      <c r="I237" s="11" t="s">
         <v>359</v>
       </c>
       <c r="J237" s="32" t="s">
         <v>360</v>
       </c>
       <c r="K237" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="250" spans="5:8">
-      <c r="E250" s="32"/>
-      <c r="F250" s="32"/>
-      <c r="G250" s="32"/>
-      <c r="H250" s="32"/>
-    </row>
-    <row r="266" spans="5:8">
-      <c r="E266" s="32"/>
-      <c r="F266" s="32"/>
-      <c r="G266" s="32"/>
-      <c r="H266" s="32"/>
-    </row>
-    <row r="274" spans="5:10">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" ht="28.8">
+      <c r="A238" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J238" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="K238" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" ht="28.8">
+      <c r="A239" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J239" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="K239" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" ht="28.8">
+      <c r="A240" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J240" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="K240" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" ht="28.8">
+      <c r="A241" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J241" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="K241" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" ht="28.8">
+      <c r="A242" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E242" s="32"/>
+      <c r="F242" s="32"/>
+      <c r="G242" s="32"/>
+      <c r="H242" s="32"/>
+      <c r="I242" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="J242" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="K242" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" ht="28.8">
+      <c r="A243" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E243" s="32"/>
+      <c r="F243" s="32"/>
+      <c r="G243" s="32"/>
+      <c r="H243" s="32"/>
+      <c r="I243" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J243" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="K243" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" ht="28.8">
+      <c r="A244" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="J244" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="K244" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" ht="28.8">
+      <c r="A245" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="I245" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J245" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="K245" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="258" spans="5:8">
+      <c r="E258" s="32"/>
+      <c r="F258" s="32"/>
+      <c r="G258" s="32"/>
+      <c r="H258" s="32"/>
+    </row>
+    <row r="274" spans="5:8">
       <c r="E274" s="32"/>
       <c r="F274" s="32"/>
       <c r="G274" s="32"/>
       <c r="H274" s="32"/>
     </row>
-    <row r="283" spans="5:10">
-      <c r="J283" s="32"/>
-    </row>
-    <row r="284" spans="5:10">
-      <c r="J284" s="32"/>
-    </row>
-    <row r="285" spans="5:10">
-      <c r="J285" s="32"/>
-    </row>
-    <row r="286" spans="5:10">
-      <c r="J286" s="32"/>
-    </row>
-    <row r="287" spans="5:10">
-      <c r="J287" s="32"/>
-    </row>
-    <row r="288" spans="5:10">
-      <c r="J288" s="32"/>
-    </row>
-    <row r="289" spans="5:10">
-      <c r="J289" s="32"/>
-    </row>
-    <row r="290" spans="5:10">
-      <c r="J290" s="32"/>
-    </row>
-    <row r="291" spans="5:10">
+    <row r="282" spans="5:8">
+      <c r="E282" s="32"/>
+      <c r="F282" s="32"/>
+      <c r="G282" s="32"/>
+      <c r="H282" s="32"/>
+    </row>
+    <row r="291" spans="10:10">
       <c r="J291" s="32"/>
     </row>
-    <row r="292" spans="5:10">
+    <row r="292" spans="10:10">
       <c r="J292" s="32"/>
     </row>
-    <row r="293" spans="5:10">
+    <row r="293" spans="10:10">
       <c r="J293" s="32"/>
     </row>
-    <row r="294" spans="5:10">
+    <row r="294" spans="10:10">
       <c r="J294" s="32"/>
     </row>
-    <row r="295" spans="5:10">
+    <row r="295" spans="10:10">
       <c r="J295" s="32"/>
     </row>
-    <row r="296" spans="5:10">
+    <row r="296" spans="10:10">
       <c r="J296" s="32"/>
     </row>
-    <row r="297" spans="5:10">
+    <row r="297" spans="10:10">
       <c r="J297" s="32"/>
     </row>
-    <row r="298" spans="5:10">
+    <row r="298" spans="10:10">
       <c r="J298" s="32"/>
     </row>
-    <row r="299" spans="5:10">
+    <row r="299" spans="10:10">
       <c r="J299" s="32"/>
     </row>
-    <row r="300" spans="5:10">
+    <row r="300" spans="10:10">
       <c r="J300" s="32"/>
     </row>
-    <row r="301" spans="5:10">
+    <row r="301" spans="10:10">
       <c r="J301" s="32"/>
     </row>
-    <row r="302" spans="5:10">
-      <c r="E302" s="32"/>
-      <c r="F302" s="32"/>
-      <c r="G302" s="32"/>
-      <c r="H302" s="32"/>
+    <row r="302" spans="10:10">
       <c r="J302" s="32"/>
     </row>
-    <row r="310" spans="5:8">
+    <row r="303" spans="10:10">
+      <c r="J303" s="32"/>
+    </row>
+    <row r="304" spans="10:10">
+      <c r="J304" s="32"/>
+    </row>
+    <row r="305" spans="5:10">
+      <c r="J305" s="32"/>
+    </row>
+    <row r="306" spans="5:10">
+      <c r="J306" s="32"/>
+    </row>
+    <row r="307" spans="5:10">
+      <c r="J307" s="32"/>
+    </row>
+    <row r="308" spans="5:10">
+      <c r="J308" s="32"/>
+    </row>
+    <row r="309" spans="5:10">
+      <c r="J309" s="32"/>
+    </row>
+    <row r="310" spans="5:10">
       <c r="E310" s="32"/>
       <c r="F310" s="32"/>
       <c r="G310" s="32"/>
       <c r="H310" s="32"/>
-    </row>
-    <row r="317" spans="5:8">
-      <c r="E317" s="32"/>
-      <c r="F317" s="32"/>
-      <c r="G317" s="32"/>
-      <c r="H317" s="32"/>
+      <c r="J310" s="32"/>
+    </row>
+    <row r="318" spans="5:10">
+      <c r="E318" s="32"/>
+      <c r="F318" s="32"/>
+      <c r="G318" s="32"/>
+      <c r="H318" s="32"/>
+    </row>
+    <row r="325" spans="5:8">
+      <c r="E325" s="32"/>
+      <c r="F325" s="32"/>
+      <c r="G325" s="32"/>
+      <c r="H325" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14595,13 +14758,13 @@
         <v>279</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>857</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" t="s">
         <v>858</v>
-      </c>
-      <c r="D9" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="10" spans="1:9">
